--- a/R Markdown/resultados/populacao_historica_1950_2022.xlsx
+++ b/R Markdown/resultados/populacao_historica_1950_2022.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M136"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -424,38 +424,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Unidades territoriais	1950	1960	1970	1980	1991	2000	2010	2022</t>
+          <t>População Município de São Paulo, subprefeituras e distritos municipais 1950, 1960, 1970, 1980, 1991, 2000, 2010 e 2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unidades territoriais</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>1950</v>
-      </c>
-      <c r="D2">
-        <v>1960</v>
-      </c>
-      <c r="E2">
-        <v>1970</v>
-      </c>
-      <c r="F2">
-        <v>1980</v>
-      </c>
-      <c r="G2">
-        <v>1991</v>
-      </c>
-      <c r="H2">
-        <v>2000</v>
+          <t>População Município de São Paulo, subprefeituras e distritos municipais</t>
+        </is>
       </c>
       <c r="I2">
         <v>2010</v>
       </c>
-      <c r="J2">
-        <v>2022</v>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Distrito</t>
@@ -465,99 +444,94 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Município de São Paulo	2.151.313	3.667.899	5.924.615	8.493.226	9.646.185	10.434.252	11.253.503   	11.451.999</t>
+          <t>Unidades territoriais	1950	1960	1970	1980	1991	2000	2010	2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Município de São Paulo</t>
+          <t>Unidades territoriais</t>
         </is>
       </c>
       <c r="C3">
-        <v>2151313</v>
+        <v>1950</v>
       </c>
       <c r="D3">
-        <v>3667899</v>
+        <v>1960</v>
       </c>
       <c r="E3">
-        <v>5924615</v>
+        <v>1970</v>
       </c>
       <c r="F3">
-        <v>8493226</v>
+        <v>1980</v>
       </c>
       <c r="G3">
-        <v>9646185</v>
+        <v>1991</v>
       </c>
       <c r="H3">
-        <v>10434252</v>
+        <v>2000</v>
       </c>
       <c r="I3">
-        <v>11253503</v>
+        <v>2010</v>
       </c>
       <c r="J3">
-        <v>11451999</v>
+        <v>2022</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Distrito</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Região Centro	350.946	432.709	445.174	526.171	458.677	373.914	431.106	423.536</t>
+          <t>Município de São Paulo	2.151.313	3.667.899	5.924.615	8.493.226	9.646.185	10.434.252	11.253.503   	11.451.999</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Região Centro</t>
+          <t>Município de São Paulo</t>
         </is>
       </c>
       <c r="C4">
-        <v>350946</v>
+        <v>2151313</v>
       </c>
       <c r="D4">
-        <v>432709</v>
+        <v>3667899</v>
       </c>
       <c r="E4">
-        <v>445174</v>
+        <v>5924615</v>
       </c>
       <c r="F4">
-        <v>526171</v>
+        <v>8493226</v>
       </c>
       <c r="G4">
-        <v>458677</v>
+        <v>9646185</v>
       </c>
       <c r="H4">
-        <v>373914</v>
+        <v>10434252</v>
       </c>
       <c r="I4">
-        <v>431106</v>
+        <v>11253503</v>
       </c>
       <c r="J4">
-        <v>423536</v>
+        <v>11451999</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Região</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Região Centro</t>
+          <t>Total</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Subprefeitura Sé	350.946	432.709	445.174	526.171	458.677	373.914	431.106	423.536</t>
+          <t>Região Centro	350.946	432.709	445.174	526.171	458.677	373.914	431.106	423.536</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Subprefeitura Sé</t>
+          <t>Região Centro</t>
         </is>
       </c>
       <c r="C5">
@@ -586,58 +560,53 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Região</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>Região Centro</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Subprefeitura Sé</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bela Vista	46.340	57.364	64.704	85.416	71.825	62.556	69.460	60.024</t>
+          <t>Subprefeitura Sé	350.946	432.709	445.174	526.171	458.677	373.914	431.106	423.536</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bela Vista</t>
+          <t>Subprefeitura Sé</t>
         </is>
       </c>
       <c r="C6">
-        <v>46340</v>
+        <v>350946</v>
       </c>
       <c r="D6">
-        <v>57364</v>
+        <v>432709</v>
       </c>
       <c r="E6">
-        <v>64704</v>
+        <v>445174</v>
       </c>
       <c r="F6">
-        <v>85416</v>
+        <v>526171</v>
       </c>
       <c r="G6">
-        <v>71825</v>
+        <v>458677</v>
       </c>
       <c r="H6">
-        <v>62556</v>
+        <v>373914</v>
       </c>
       <c r="I6">
-        <v>69460</v>
+        <v>431106</v>
       </c>
       <c r="J6">
-        <v>60024</v>
+        <v>423536</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -654,37 +623,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bom Retiro	45.880	53.893	45.662	47.588	36.136	26.598	33.892	33.520</t>
+          <t>Bela Vista	46.340	57.364	64.704	85.416	71.825	62.556	69.460	60.024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bom Retiro</t>
+          <t>Bela Vista</t>
         </is>
       </c>
       <c r="C7">
-        <v>45880</v>
+        <v>46340</v>
       </c>
       <c r="D7">
-        <v>53893</v>
+        <v>57364</v>
       </c>
       <c r="E7">
-        <v>45662</v>
+        <v>64704</v>
       </c>
       <c r="F7">
-        <v>47588</v>
+        <v>85416</v>
       </c>
       <c r="G7">
-        <v>36136</v>
+        <v>71825</v>
       </c>
       <c r="H7">
-        <v>26598</v>
+        <v>62556</v>
       </c>
       <c r="I7">
-        <v>33892</v>
+        <v>69460</v>
       </c>
       <c r="J7">
-        <v>33520</v>
+        <v>60024</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -705,37 +674,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cambuci	35.499	39.789	39.727	44.851	37.069	28.717	36.948	45.163</t>
+          <t>Bom Retiro	45.880	53.893	45.662	47.588	36.136	26.598	33.892	33.520</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cambuci</t>
+          <t>Bom Retiro</t>
         </is>
       </c>
       <c r="C8">
-        <v>35499</v>
+        <v>45880</v>
       </c>
       <c r="D8">
-        <v>39789</v>
+        <v>53893</v>
       </c>
       <c r="E8">
-        <v>39727</v>
+        <v>45662</v>
       </c>
       <c r="F8">
-        <v>44851</v>
+        <v>47588</v>
       </c>
       <c r="G8">
-        <v>37069</v>
+        <v>36136</v>
       </c>
       <c r="H8">
-        <v>28717</v>
+        <v>26598</v>
       </c>
       <c r="I8">
-        <v>36948</v>
+        <v>33892</v>
       </c>
       <c r="J8">
-        <v>45163</v>
+        <v>33520</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -756,37 +725,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Consolação	38.228	52.182	60.600	77.338	66.590	54.522	57.365	53.249</t>
+          <t>Cambuci	35.499	39.789	39.727	44.851	37.069	28.717	36.948	45.163</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Consolação</t>
+          <t>Cambuci</t>
         </is>
       </c>
       <c r="C9">
-        <v>38228</v>
+        <v>35499</v>
       </c>
       <c r="D9">
-        <v>52182</v>
+        <v>39789</v>
       </c>
       <c r="E9">
-        <v>60600</v>
+        <v>39727</v>
       </c>
       <c r="F9">
-        <v>77338</v>
+        <v>44851</v>
       </c>
       <c r="G9">
-        <v>66590</v>
+        <v>37069</v>
       </c>
       <c r="H9">
-        <v>54522</v>
+        <v>28717</v>
       </c>
       <c r="I9">
-        <v>57365</v>
+        <v>36948</v>
       </c>
       <c r="J9">
-        <v>53249</v>
+        <v>45163</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -807,37 +776,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Liberdade	55.523	68.210	71.503	82.472	76.245	61.875	69.092	66.056</t>
+          <t>Consolação	38.228	52.182	60.600	77.338	66.590	54.522	57.365	53.249</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Liberdade</t>
+          <t>Consolação</t>
         </is>
       </c>
       <c r="C10">
-        <v>55523</v>
+        <v>38228</v>
       </c>
       <c r="D10">
-        <v>68210</v>
+        <v>52182</v>
       </c>
       <c r="E10">
-        <v>71503</v>
+        <v>60600</v>
       </c>
       <c r="F10">
-        <v>82472</v>
+        <v>77338</v>
       </c>
       <c r="G10">
-        <v>76245</v>
+        <v>66590</v>
       </c>
       <c r="H10">
-        <v>61875</v>
+        <v>54522</v>
       </c>
       <c r="I10">
-        <v>69092</v>
+        <v>57365</v>
       </c>
       <c r="J10">
-        <v>66056</v>
+        <v>53249</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -858,37 +827,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>República	35.994	48.347	50.348	60.999	57.797	48.352	57.341	60.720</t>
+          <t>Liberdade	46.216	54.673	53.230	56.732	61.026	56.402	69.092	76.549</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>República</t>
+          <t>Liberdade</t>
         </is>
       </c>
       <c r="C11">
-        <v>35994</v>
+        <v>46216</v>
       </c>
       <c r="D11">
-        <v>48347</v>
+        <v>54673</v>
       </c>
       <c r="E11">
-        <v>50348</v>
+        <v>53230</v>
       </c>
       <c r="F11">
-        <v>60999</v>
+        <v>56732</v>
       </c>
       <c r="G11">
-        <v>57797</v>
+        <v>61026</v>
       </c>
       <c r="H11">
-        <v>48352</v>
+        <v>56402</v>
       </c>
       <c r="I11">
-        <v>57341</v>
+        <v>69092</v>
       </c>
       <c r="J11">
-        <v>60720</v>
+        <v>76549</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -909,37 +878,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Santa Cecília	63.460	80.581	83.075	94.542	85.829	71.179	83.357	80.972</t>
+          <t>República	44.606	51.794	46.547	54.835	49.493	41.045	56.981	58.745</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Santa Cecília</t>
+          <t>República</t>
         </is>
       </c>
       <c r="C12">
-        <v>63460</v>
+        <v>44606</v>
       </c>
       <c r="D12">
-        <v>80581</v>
+        <v>51794</v>
       </c>
       <c r="E12">
-        <v>83075</v>
+        <v>46547</v>
       </c>
       <c r="F12">
-        <v>94542</v>
+        <v>54835</v>
       </c>
       <c r="G12">
-        <v>85829</v>
+        <v>49493</v>
       </c>
       <c r="H12">
-        <v>71179</v>
+        <v>41045</v>
       </c>
       <c r="I12">
-        <v>83357</v>
+        <v>56981</v>
       </c>
       <c r="J12">
-        <v>80972</v>
+        <v>58745</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -960,37 +929,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sé	30.022	32.343	29.555	32.965	27.186	20.115	23.651	23.832</t>
+          <t>Santa Cecília	67.147	85.503	89.658	103.559	91.077	76.242	83.715	84.721</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sé</t>
+          <t>Santa Cecília</t>
         </is>
       </c>
       <c r="C13">
-        <v>30022</v>
+        <v>67147</v>
       </c>
       <c r="D13">
-        <v>32343</v>
+        <v>85503</v>
       </c>
       <c r="E13">
-        <v>29555</v>
+        <v>89658</v>
       </c>
       <c r="F13">
-        <v>32965</v>
+        <v>103559</v>
       </c>
       <c r="G13">
-        <v>27186</v>
+        <v>91077</v>
       </c>
       <c r="H13">
-        <v>20115</v>
+        <v>76242</v>
       </c>
       <c r="I13">
-        <v>23651</v>
+        <v>83715</v>
       </c>
       <c r="J13">
-        <v>23832</v>
+        <v>84721</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1011,46 +980,46 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Região Leste	672.876	1.169.131	1.989.676	2.877.590	3.465.397	3.835.354	3.998.237	3.991.262</t>
+          <t>Sé	27.030	37.511	35.046	45.852	45.461	27.832	23.653	11.585</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Região Leste</t>
+          <t>Sé</t>
         </is>
       </c>
       <c r="C14">
-        <v>672876</v>
+        <v>27030</v>
       </c>
       <c r="D14">
-        <v>1169131</v>
+        <v>37511</v>
       </c>
       <c r="E14">
-        <v>1989676</v>
+        <v>35046</v>
       </c>
       <c r="F14">
-        <v>2877590</v>
+        <v>45852</v>
       </c>
       <c r="G14">
-        <v>3465397</v>
+        <v>45461</v>
       </c>
       <c r="H14">
-        <v>3835354</v>
+        <v>27832</v>
       </c>
       <c r="I14">
-        <v>3998237</v>
+        <v>23653</v>
       </c>
       <c r="J14">
-        <v>3991262</v>
+        <v>11585</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Região</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Região Leste</t>
+          <t>Região Centro</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1062,41 +1031,41 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Subprefeitura Aricanduva-Formosa-Carrão	112.431	194.578	265.532	298.116	281.788	267.780	267.702	266.157</t>
+          <t>Região Leste	368.187	866.598	1.670.368	2.443.085	3.241.134	3.812.359	3.968.127	3.991.262</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Subprefeitura Aricanduva-Formosa-Carrão</t>
+          <t>Região Leste</t>
         </is>
       </c>
       <c r="C15">
-        <v>112431</v>
+        <v>368187</v>
       </c>
       <c r="D15">
-        <v>194578</v>
+        <v>866598</v>
       </c>
       <c r="E15">
-        <v>265532</v>
+        <v>1670368</v>
       </c>
       <c r="F15">
-        <v>298116</v>
+        <v>2443085</v>
       </c>
       <c r="G15">
-        <v>281788</v>
+        <v>3241134</v>
       </c>
       <c r="H15">
-        <v>267780</v>
+        <v>3812359</v>
       </c>
       <c r="I15">
-        <v>267702</v>
+        <v>3968127</v>
       </c>
       <c r="J15">
-        <v>266157</v>
+        <v>3991262</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Região</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1106,48 +1075,48 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Subprefeitura Aricanduva-Formosa-Carrão</t>
+          <t>Subprefeitura Sé</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Aricanduva	32.318	58.076	81.577	92.790	96.512	95.258	89.622	89.574</t>
+          <t>Subprefeitura Aricanduva-Formosa-Carrão	31.060	67.755	114.735	163.666	194.218	259.651	267.702	266.497</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aricanduva</t>
+          <t>Subprefeitura Aricanduva-Formosa-Carrão</t>
         </is>
       </c>
       <c r="C16">
-        <v>32318</v>
+        <v>31060</v>
       </c>
       <c r="D16">
-        <v>58076</v>
+        <v>67755</v>
       </c>
       <c r="E16">
-        <v>81577</v>
+        <v>114735</v>
       </c>
       <c r="F16">
-        <v>92790</v>
+        <v>163666</v>
       </c>
       <c r="G16">
-        <v>96512</v>
+        <v>194218</v>
       </c>
       <c r="H16">
-        <v>95258</v>
+        <v>259651</v>
       </c>
       <c r="I16">
-        <v>89622</v>
+        <v>267702</v>
       </c>
       <c r="J16">
-        <v>89574</v>
+        <v>266497</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1164,37 +1133,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Carrão	34.556	62.098	87.228	99.218	87.336	78.175	83.281	84.397</t>
+          <t>Aricanduva	7.025	15.334	36.002	63.627	76.417	89.510	89.622	92.684</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carrão</t>
+          <t>Aricanduva</t>
         </is>
       </c>
       <c r="C17">
-        <v>34556</v>
+        <v>7025</v>
       </c>
       <c r="D17">
-        <v>62098</v>
+        <v>15334</v>
       </c>
       <c r="E17">
-        <v>87228</v>
+        <v>36002</v>
       </c>
       <c r="F17">
-        <v>99218</v>
+        <v>63627</v>
       </c>
       <c r="G17">
-        <v>87336</v>
+        <v>76417</v>
       </c>
       <c r="H17">
-        <v>78175</v>
+        <v>89510</v>
       </c>
       <c r="I17">
-        <v>83281</v>
+        <v>89622</v>
       </c>
       <c r="J17">
-        <v>84397</v>
+        <v>92684</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1215,37 +1184,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Vila Formosa	45.557	74.404	96.727	106.108	97.940	94.347	94.799	92.186</t>
+          <t>Carrão	10.871	23.714	31.942	39.697	41.527	75.787	83.281	83.076</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vila Formosa</t>
+          <t>Carrão</t>
         </is>
       </c>
       <c r="C18">
-        <v>45557</v>
+        <v>10871</v>
       </c>
       <c r="D18">
-        <v>74404</v>
+        <v>23714</v>
       </c>
       <c r="E18">
-        <v>96727</v>
+        <v>31942</v>
       </c>
       <c r="F18">
-        <v>106108</v>
+        <v>39697</v>
       </c>
       <c r="G18">
-        <v>97940</v>
+        <v>41527</v>
       </c>
       <c r="H18">
-        <v>94347</v>
+        <v>75787</v>
       </c>
       <c r="I18">
-        <v>94799</v>
+        <v>83281</v>
       </c>
       <c r="J18">
-        <v>92186</v>
+        <v>83076</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1266,41 +1235,41 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Subprefeitura Cidade Tiradentes	599	1.418	4.296	8.603	96.281	190.657	211.501	194.177</t>
+          <t>Vila Formosa	13.164	28.707	46.791	60.342	76.274	94.354	94.799	90.737</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Subprefeitura Cidade Tiradentes</t>
+          <t>Vila Formosa</t>
         </is>
       </c>
       <c r="C19">
-        <v>599</v>
+        <v>13164</v>
       </c>
       <c r="D19">
-        <v>1418</v>
+        <v>28707</v>
       </c>
       <c r="E19">
-        <v>4296</v>
+        <v>46791</v>
       </c>
       <c r="F19">
-        <v>8603</v>
+        <v>60342</v>
       </c>
       <c r="G19">
-        <v>96281</v>
+        <v>76274</v>
       </c>
       <c r="H19">
-        <v>190657</v>
+        <v>94354</v>
       </c>
       <c r="I19">
-        <v>211501</v>
+        <v>94799</v>
       </c>
       <c r="J19">
-        <v>194177</v>
+        <v>90737</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1310,48 +1279,48 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Subprefeitura Cidade Tiradentes</t>
+          <t>Subprefeitura Aricanduva-Formosa-Carrão</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cidade Tiradentes	599	1.418	4.296	8.603	96.281	190.657	211.501	194.177</t>
+          <t>Subprefeitura Cidade Tiradentes	7.289	17.135	43.433	71.218	108.625	190.505	211.503	187.216</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cidade Tiradentes</t>
+          <t>Subprefeitura Cidade Tiradentes</t>
         </is>
       </c>
       <c r="C20">
-        <v>599</v>
+        <v>7289</v>
       </c>
       <c r="D20">
-        <v>1418</v>
+        <v>17135</v>
       </c>
       <c r="E20">
-        <v>4296</v>
+        <v>43433</v>
       </c>
       <c r="F20">
-        <v>8603</v>
+        <v>71218</v>
       </c>
       <c r="G20">
-        <v>96281</v>
+        <v>108625</v>
       </c>
       <c r="H20">
-        <v>190657</v>
+        <v>190505</v>
       </c>
       <c r="I20">
-        <v>211501</v>
+        <v>211503</v>
       </c>
       <c r="J20">
-        <v>194177</v>
+        <v>187216</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1368,41 +1337,41 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Subprefeitura Ermelino Matarazzo	19.040	67.160	112.031	177.307	198.311	204.951	207.273	202.214</t>
+          <t>Cidade Tiradentes	7.289	17.135	43.433	71.218	108.625	190.505	211.503	187.216</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Subprefeitura Ermelino Matarazzo</t>
+          <t>Cidade Tiradentes</t>
         </is>
       </c>
       <c r="C21">
-        <v>19040</v>
+        <v>7289</v>
       </c>
       <c r="D21">
-        <v>67160</v>
+        <v>17135</v>
       </c>
       <c r="E21">
-        <v>112031</v>
+        <v>43433</v>
       </c>
       <c r="F21">
-        <v>177307</v>
+        <v>71218</v>
       </c>
       <c r="G21">
-        <v>198311</v>
+        <v>108625</v>
       </c>
       <c r="H21">
-        <v>204951</v>
+        <v>190505</v>
       </c>
       <c r="I21">
-        <v>207273</v>
+        <v>211503</v>
       </c>
       <c r="J21">
-        <v>202214</v>
+        <v>187216</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1412,48 +1381,48 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Subprefeitura Ermelino Matarazzo</t>
+          <t>Subprefeitura Cidade Tiradentes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ermelino Matarazzo	10.835	38.218	50.872	80.513	95.609	106.838	113.379	112.333</t>
+          <t>Subprefeitura Ermelino Matarazzo	13.435	41.258	96.345	134.502	144.598	201.272	207.603	203.874</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ermelino Matarazzo</t>
+          <t>Subprefeitura Ermelino Matarazzo</t>
         </is>
       </c>
       <c r="C22">
-        <v>10835</v>
+        <v>13435</v>
       </c>
       <c r="D22">
-        <v>38218</v>
+        <v>41258</v>
       </c>
       <c r="E22">
-        <v>50872</v>
+        <v>96345</v>
       </c>
       <c r="F22">
-        <v>80513</v>
+        <v>134502</v>
       </c>
       <c r="G22">
-        <v>95609</v>
+        <v>144598</v>
       </c>
       <c r="H22">
-        <v>106838</v>
+        <v>201272</v>
       </c>
       <c r="I22">
-        <v>113379</v>
+        <v>207603</v>
       </c>
       <c r="J22">
-        <v>112333</v>
+        <v>203874</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1470,37 +1439,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ponte Rasa	8.205	28.942	61.159	96.794	102.702	98.113	93.894	89.881</t>
+          <t>Ermelino Matarazzo	8.061	24.755	57.807	80.701	86.759	116.409	113.615	108.972</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ponte Rasa</t>
+          <t>Ermelino Matarazzo</t>
         </is>
       </c>
       <c r="C23">
-        <v>8205</v>
+        <v>8061</v>
       </c>
       <c r="D23">
-        <v>28942</v>
+        <v>24755</v>
       </c>
       <c r="E23">
-        <v>61159</v>
+        <v>57807</v>
       </c>
       <c r="F23">
-        <v>96794</v>
+        <v>80701</v>
       </c>
       <c r="G23">
-        <v>102702</v>
+        <v>86759</v>
       </c>
       <c r="H23">
-        <v>98113</v>
+        <v>116409</v>
       </c>
       <c r="I23">
-        <v>93894</v>
+        <v>113615</v>
       </c>
       <c r="J23">
-        <v>89881</v>
+        <v>108972</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1521,41 +1490,41 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Subprefeitura Guaianases	6.705	17.290	59.749	119.835	194.180	256.319	268.508	273.707</t>
+          <t>Ponte Rasa	5.374	16.503	38.538	53.801	57.839	84.863	93.988	94.902</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Subprefeitura Guaianases</t>
+          <t>Ponte Rasa</t>
         </is>
       </c>
       <c r="C24">
-        <v>6705</v>
+        <v>5374</v>
       </c>
       <c r="D24">
-        <v>17290</v>
+        <v>16503</v>
       </c>
       <c r="E24">
-        <v>59749</v>
+        <v>38538</v>
       </c>
       <c r="F24">
-        <v>119835</v>
+        <v>53801</v>
       </c>
       <c r="G24">
-        <v>194180</v>
+        <v>57839</v>
       </c>
       <c r="H24">
-        <v>256319</v>
+        <v>84863</v>
       </c>
       <c r="I24">
-        <v>268508</v>
+        <v>93988</v>
       </c>
       <c r="J24">
-        <v>273707</v>
+        <v>94902</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1565,48 +1534,48 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Subprefeitura Guaianases</t>
+          <t>Subprefeitura Ermelino Matarazzo</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Guaianases	3.510	8.311	25.177	50.417	81.373	98.546	103.996	109.316</t>
+          <t>Subprefeitura Guaianases	11.332	26.638	67.525	110.723	161.801	255.441	284.530	276.378</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Guaianases</t>
+          <t>Subprefeitura Guaianases</t>
         </is>
       </c>
       <c r="C25">
-        <v>3510</v>
+        <v>11332</v>
       </c>
       <c r="D25">
-        <v>8311</v>
+        <v>26638</v>
       </c>
       <c r="E25">
-        <v>25177</v>
+        <v>67525</v>
       </c>
       <c r="F25">
-        <v>50417</v>
+        <v>110723</v>
       </c>
       <c r="G25">
-        <v>81373</v>
+        <v>161801</v>
       </c>
       <c r="H25">
-        <v>98546</v>
+        <v>255441</v>
       </c>
       <c r="I25">
-        <v>103996</v>
+        <v>284530</v>
       </c>
       <c r="J25">
-        <v>109316</v>
+        <v>276378</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1623,37 +1592,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lajeado	3.195	8.979	34.572	69.418	112.807	157.773	164.512	164.391</t>
+          <t>Guaianases	6.799	15.983	40.515	66.434	97.081	103.541	105.242	98.675</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lajeado</t>
+          <t>Guaianases</t>
         </is>
       </c>
       <c r="C26">
-        <v>3195</v>
+        <v>6799</v>
       </c>
       <c r="D26">
-        <v>8979</v>
+        <v>15983</v>
       </c>
       <c r="E26">
-        <v>34572</v>
+        <v>40515</v>
       </c>
       <c r="F26">
-        <v>69418</v>
+        <v>66434</v>
       </c>
       <c r="G26">
-        <v>112807</v>
+        <v>97081</v>
       </c>
       <c r="H26">
-        <v>157773</v>
+        <v>103541</v>
       </c>
       <c r="I26">
-        <v>164512</v>
+        <v>105242</v>
       </c>
       <c r="J26">
-        <v>164391</v>
+        <v>98675</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1674,41 +1643,41 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Subprefeitura Itaim Paulista	12.721	32.599	102.779	202.710	287.569	358.709	372.759	345.968</t>
+          <t>Lajeado	4.533	10.655	27.010	44.289	64.720	151.900	179.288	177.703</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Subprefeitura Itaim Paulista</t>
+          <t>Lajeado</t>
         </is>
       </c>
       <c r="C27">
-        <v>12721</v>
+        <v>4533</v>
       </c>
       <c r="D27">
-        <v>32599</v>
+        <v>10655</v>
       </c>
       <c r="E27">
-        <v>102779</v>
+        <v>27010</v>
       </c>
       <c r="F27">
-        <v>202710</v>
+        <v>44289</v>
       </c>
       <c r="G27">
-        <v>287569</v>
+        <v>64720</v>
       </c>
       <c r="H27">
-        <v>358709</v>
+        <v>151900</v>
       </c>
       <c r="I27">
-        <v>372759</v>
+        <v>179288</v>
       </c>
       <c r="J27">
-        <v>345968</v>
+        <v>177703</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1718,48 +1687,48 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Subprefeitura Itaim Paulista</t>
+          <t>Subprefeitura Guaianases</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itaim Paulista	6.077	16.865	55.113	107.259	163.269	212.733	224.074	205.295</t>
+          <t>Subprefeitura Itaim Paulista	15.865	37.291	94.526	155.000	226.495	358.553	373.112	372.134</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Itaim Paulista</t>
+          <t>Subprefeitura Itaim Paulista</t>
         </is>
       </c>
       <c r="C28">
-        <v>6077</v>
+        <v>15865</v>
       </c>
       <c r="D28">
-        <v>16865</v>
+        <v>37291</v>
       </c>
       <c r="E28">
-        <v>55113</v>
+        <v>94526</v>
       </c>
       <c r="F28">
-        <v>107259</v>
+        <v>155000</v>
       </c>
       <c r="G28">
-        <v>163269</v>
+        <v>226495</v>
       </c>
       <c r="H28">
-        <v>212733</v>
+        <v>358553</v>
       </c>
       <c r="I28">
-        <v>224074</v>
+        <v>373112</v>
       </c>
       <c r="J28">
-        <v>205295</v>
+        <v>372134</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1776,37 +1745,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Vila Curuçá	6.644	15.734	47.666	95.451	124.300	145.976	148.685	140.673</t>
+          <t>Itaim Paulista	9.519	22.375	56.716	93.000	135.897	210.871	224.074	228.636</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vila Curuçá</t>
+          <t>Itaim Paulista</t>
         </is>
       </c>
       <c r="C29">
-        <v>6644</v>
+        <v>9519</v>
       </c>
       <c r="D29">
-        <v>15734</v>
+        <v>22375</v>
       </c>
       <c r="E29">
-        <v>47666</v>
+        <v>56716</v>
       </c>
       <c r="F29">
-        <v>95451</v>
+        <v>93000</v>
       </c>
       <c r="G29">
-        <v>124300</v>
+        <v>135897</v>
       </c>
       <c r="H29">
-        <v>145976</v>
+        <v>210871</v>
       </c>
       <c r="I29">
-        <v>148685</v>
+        <v>224074</v>
       </c>
       <c r="J29">
-        <v>140673</v>
+        <v>228636</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1827,41 +1796,41 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Subprefeitura Itaquera	15.245	36.964	129.314	256.383	431.191	489.502	523.848	550.540</t>
+          <t>Vila Curuçá	6.346	14.916	37.810	62.000	90.598	147.682	149.038	143.498</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Subprefeitura Itaquera</t>
+          <t>Vila Curuçá</t>
         </is>
       </c>
       <c r="C30">
-        <v>15245</v>
+        <v>6346</v>
       </c>
       <c r="D30">
-        <v>36964</v>
+        <v>14916</v>
       </c>
       <c r="E30">
-        <v>129314</v>
+        <v>37810</v>
       </c>
       <c r="F30">
-        <v>256383</v>
+        <v>62000</v>
       </c>
       <c r="G30">
-        <v>431191</v>
+        <v>90598</v>
       </c>
       <c r="H30">
-        <v>489502</v>
+        <v>147682</v>
       </c>
       <c r="I30">
-        <v>523848</v>
+        <v>149038</v>
       </c>
       <c r="J30">
-        <v>550540</v>
+        <v>143498</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -1871,48 +1840,48 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Subprefeitura Itaquera</t>
+          <t>Subprefeitura Itaim Paulista</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cidade Lider	7.254	15.064	38.420	70.508	97.370	115.329	126.597	136.660</t>
+          <t>Subprefeitura Itaquera	43.619	102.531	260.231	426.711	451.972	488.324	523.263	501.306</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cidade Lider</t>
+          <t>Subprefeitura Itaquera</t>
         </is>
       </c>
       <c r="C31">
-        <v>7254</v>
+        <v>43619</v>
       </c>
       <c r="D31">
-        <v>15064</v>
+        <v>102531</v>
       </c>
       <c r="E31">
-        <v>38420</v>
+        <v>260231</v>
       </c>
       <c r="F31">
-        <v>70508</v>
+        <v>426711</v>
       </c>
       <c r="G31">
-        <v>97370</v>
+        <v>451972</v>
       </c>
       <c r="H31">
-        <v>115329</v>
+        <v>488324</v>
       </c>
       <c r="I31">
-        <v>126597</v>
+        <v>523263</v>
       </c>
       <c r="J31">
-        <v>136660</v>
+        <v>501306</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -1929,37 +1898,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Itaquera	5.070	15.245	63.070	126.727	175.366	203.024	204.871	210.960</t>
+          <t>Cidade Líder	11.341	26.658	67.659	110.943	120.301	126.597	126.566	124.770</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Itaquera</t>
+          <t>Cidade Líder</t>
         </is>
       </c>
       <c r="C32">
-        <v>5070</v>
+        <v>11341</v>
       </c>
       <c r="D32">
-        <v>15245</v>
+        <v>26658</v>
       </c>
       <c r="E32">
-        <v>63070</v>
+        <v>67659</v>
       </c>
       <c r="F32">
-        <v>126727</v>
+        <v>110943</v>
       </c>
       <c r="G32">
-        <v>175366</v>
+        <v>120301</v>
       </c>
       <c r="H32">
-        <v>203024</v>
+        <v>126597</v>
       </c>
       <c r="I32">
-        <v>204871</v>
+        <v>126566</v>
       </c>
       <c r="J32">
-        <v>210960</v>
+        <v>124770</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -1980,37 +1949,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>José Bonifácio	1.188	2.706	11.313	24.049	103.712	107.082	124.122	128.243</t>
+          <t>Itaquera	10.905	25.633	65.058	106.679	116.712	188.751	204.871	210.040</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>José Bonifácio</t>
+          <t>Itaquera</t>
         </is>
       </c>
       <c r="C33">
-        <v>1188</v>
+        <v>10905</v>
       </c>
       <c r="D33">
-        <v>2706</v>
+        <v>25633</v>
       </c>
       <c r="E33">
-        <v>11313</v>
+        <v>65058</v>
       </c>
       <c r="F33">
-        <v>24049</v>
+        <v>106679</v>
       </c>
       <c r="G33">
-        <v>103712</v>
+        <v>116712</v>
       </c>
       <c r="H33">
-        <v>107082</v>
+        <v>188751</v>
       </c>
       <c r="I33">
-        <v>124122</v>
+        <v>204871</v>
       </c>
       <c r="J33">
-        <v>128243</v>
+        <v>210040</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2031,37 +2000,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Parque do Carmo	1.733	3.949	16.511	35.099	54.743	64.067	68.258	74.677</t>
+          <t>José Bonifácio	10.905	25.633	65.058	106.679	104.992	108.633	124.122	122.955</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Parque do Carmo</t>
+          <t>José Bonifácio</t>
         </is>
       </c>
       <c r="C34">
-        <v>1733</v>
+        <v>10905</v>
       </c>
       <c r="D34">
-        <v>3949</v>
+        <v>25633</v>
       </c>
       <c r="E34">
-        <v>16511</v>
+        <v>65058</v>
       </c>
       <c r="F34">
-        <v>35099</v>
+        <v>106679</v>
       </c>
       <c r="G34">
-        <v>54743</v>
+        <v>104992</v>
       </c>
       <c r="H34">
-        <v>64067</v>
+        <v>108633</v>
       </c>
       <c r="I34">
-        <v>68258</v>
+        <v>124122</v>
       </c>
       <c r="J34">
-        <v>74677</v>
+        <v>122955</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2082,41 +2051,41 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Subprefeitura Mooca	262.891	334.691	384.801	409.374	353.470	308.161	343.980	377.163</t>
+          <t>Parque do Carmo	10.468	24.607	62.456	102.410	109.967	64.343	67.704	43.541</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Subprefeitura Mooca</t>
+          <t>Parque do Carmo</t>
         </is>
       </c>
       <c r="C35">
-        <v>262891</v>
+        <v>10468</v>
       </c>
       <c r="D35">
-        <v>334691</v>
+        <v>24607</v>
       </c>
       <c r="E35">
-        <v>384801</v>
+        <v>62456</v>
       </c>
       <c r="F35">
-        <v>409374</v>
+        <v>102410</v>
       </c>
       <c r="G35">
-        <v>353470</v>
+        <v>109967</v>
       </c>
       <c r="H35">
-        <v>308161</v>
+        <v>64343</v>
       </c>
       <c r="I35">
-        <v>343980</v>
+        <v>67704</v>
       </c>
       <c r="J35">
-        <v>377163</v>
+        <v>43541</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2126,48 +2095,48 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Subprefeitura Mooca</t>
+          <t>Subprefeitura Itaquera</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Água Rasa	38.959	66.763	96.187	112.609	95.099	85.896	84.963	85.788</t>
+          <t>Subprefeitura Mooca	102.962	242.023	342.368	434.502	344.020	305.436	343.980	354.316</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Água Rasa</t>
+          <t>Subprefeitura Mooca</t>
         </is>
       </c>
       <c r="C36">
-        <v>38959</v>
+        <v>102962</v>
       </c>
       <c r="D36">
-        <v>66763</v>
+        <v>242023</v>
       </c>
       <c r="E36">
-        <v>96187</v>
+        <v>342368</v>
       </c>
       <c r="F36">
-        <v>112609</v>
+        <v>434502</v>
       </c>
       <c r="G36">
-        <v>95099</v>
+        <v>344020</v>
       </c>
       <c r="H36">
-        <v>85896</v>
+        <v>305436</v>
       </c>
       <c r="I36">
-        <v>84963</v>
+        <v>343980</v>
       </c>
       <c r="J36">
-        <v>85788</v>
+        <v>354316</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2184,37 +2153,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Belém	56.722	62.881	60.031	57.195	49.697	39.622	45.057	55.785</t>
+          <t>Água Rasa	26.241	61.683	75.525	95.590	90.076	84.346	84.968	80.932</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Belém</t>
+          <t>Água Rasa</t>
         </is>
       </c>
       <c r="C37">
-        <v>56722</v>
+        <v>26241</v>
       </c>
       <c r="D37">
-        <v>62881</v>
+        <v>61683</v>
       </c>
       <c r="E37">
-        <v>60031</v>
+        <v>75525</v>
       </c>
       <c r="F37">
-        <v>57195</v>
+        <v>95590</v>
       </c>
       <c r="G37">
-        <v>49697</v>
+        <v>90076</v>
       </c>
       <c r="H37">
-        <v>39622</v>
+        <v>84346</v>
       </c>
       <c r="I37">
-        <v>45057</v>
+        <v>84968</v>
       </c>
       <c r="J37">
-        <v>55785</v>
+        <v>80932</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2235,37 +2204,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Brás	55.097	48.875	41.006	38.630	33.536	25.158	29.265	38.750</t>
+          <t>Belém	15.444	36.303	44.448	56.245	51.603	39.261	36.283	44.004</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brás</t>
+          <t>Belém</t>
         </is>
       </c>
       <c r="C38">
-        <v>55097</v>
+        <v>15444</v>
       </c>
       <c r="D38">
-        <v>48875</v>
+        <v>36303</v>
       </c>
       <c r="E38">
-        <v>41006</v>
+        <v>44448</v>
       </c>
       <c r="F38">
-        <v>38630</v>
+        <v>56245</v>
       </c>
       <c r="G38">
-        <v>33536</v>
+        <v>51603</v>
       </c>
       <c r="H38">
-        <v>25158</v>
+        <v>39261</v>
       </c>
       <c r="I38">
-        <v>29265</v>
+        <v>36283</v>
       </c>
       <c r="J38">
-        <v>38750</v>
+        <v>44004</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2286,37 +2255,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mooca	46.679	61.973	74.386	84.583	71.999	63.280	75.724	80.880</t>
+          <t>Brás	15.444	36.303	44.448	56.245	34.402	25.045	29.265	31.117</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mooca</t>
+          <t>Brás</t>
         </is>
       </c>
       <c r="C39">
-        <v>46679</v>
+        <v>15444</v>
       </c>
       <c r="D39">
-        <v>61973</v>
+        <v>36303</v>
       </c>
       <c r="E39">
-        <v>74386</v>
+        <v>44448</v>
       </c>
       <c r="F39">
-        <v>84583</v>
+        <v>56245</v>
       </c>
       <c r="G39">
-        <v>71999</v>
+        <v>34402</v>
       </c>
       <c r="H39">
-        <v>63280</v>
+        <v>25045</v>
       </c>
       <c r="I39">
-        <v>75724</v>
+        <v>29265</v>
       </c>
       <c r="J39">
-        <v>80880</v>
+        <v>31117</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2337,37 +2306,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Pari	31.312	33.706	29.914	26.968	21.299	14.824	17.299	17.359</t>
+          <t>Mooca	15.444	36.303	88.309	111.743	75.684	64.695	75.724	76.126</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pari</t>
+          <t>Mooca</t>
         </is>
       </c>
       <c r="C40">
-        <v>31312</v>
+        <v>15444</v>
       </c>
       <c r="D40">
-        <v>33706</v>
+        <v>36303</v>
       </c>
       <c r="E40">
-        <v>29914</v>
+        <v>88309</v>
       </c>
       <c r="F40">
-        <v>26968</v>
+        <v>111743</v>
       </c>
       <c r="G40">
-        <v>21299</v>
+        <v>75684</v>
       </c>
       <c r="H40">
-        <v>14824</v>
+        <v>64695</v>
       </c>
       <c r="I40">
-        <v>17299</v>
+        <v>75724</v>
       </c>
       <c r="J40">
-        <v>17359</v>
+        <v>76126</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2388,37 +2357,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tatuapé	34.122	60.493	83.277	89.389	81.840	79.381	91.672	98.601</t>
+          <t>Pari	15.444	36.303	44.448	56.245	23.700	14.991	17.299	19.553</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tatuapé</t>
+          <t>Pari</t>
         </is>
       </c>
       <c r="C41">
-        <v>34122</v>
+        <v>15444</v>
       </c>
       <c r="D41">
-        <v>60493</v>
+        <v>36303</v>
       </c>
       <c r="E41">
-        <v>83277</v>
+        <v>44448</v>
       </c>
       <c r="F41">
-        <v>89389</v>
+        <v>56245</v>
       </c>
       <c r="G41">
-        <v>81840</v>
+        <v>23700</v>
       </c>
       <c r="H41">
-        <v>79381</v>
+        <v>14991</v>
       </c>
       <c r="I41">
-        <v>91672</v>
+        <v>17299</v>
       </c>
       <c r="J41">
-        <v>98601</v>
+        <v>19553</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2439,41 +2408,41 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Subprefeitura Penha	105.016	206.463	336.280	462.665	475.630	475.879	474.659	472.757</t>
+          <t>Tatuapé	14.945	35.128	45.190	58.434	68.555	77.098	100.441	102.584</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Subprefeitura Penha</t>
+          <t>Tatuapé</t>
         </is>
       </c>
       <c r="C42">
-        <v>105016</v>
+        <v>14945</v>
       </c>
       <c r="D42">
-        <v>206463</v>
+        <v>35128</v>
       </c>
       <c r="E42">
-        <v>336280</v>
+        <v>45190</v>
       </c>
       <c r="F42">
-        <v>462665</v>
+        <v>58434</v>
       </c>
       <c r="G42">
-        <v>475630</v>
+        <v>68555</v>
       </c>
       <c r="H42">
-        <v>475879</v>
+        <v>77098</v>
       </c>
       <c r="I42">
-        <v>474659</v>
+        <v>100441</v>
       </c>
       <c r="J42">
-        <v>472757</v>
+        <v>102584</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2483,48 +2452,48 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Subprefeitura Penha</t>
+          <t>Subprefeitura Mooca</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Artur Alvim	16.549	35.396	68.637	107.130	118.531	111.210	105.269	95.575</t>
+          <t>Subprefeitura Penha	100.413	236.035	325.210	405.012	420.044	464.082	472.249	469.766</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Artur Alvim</t>
+          <t>Subprefeitura Penha</t>
         </is>
       </c>
       <c r="C43">
-        <v>16549</v>
+        <v>100413</v>
       </c>
       <c r="D43">
-        <v>35396</v>
+        <v>236035</v>
       </c>
       <c r="E43">
-        <v>68637</v>
+        <v>325210</v>
       </c>
       <c r="F43">
-        <v>107130</v>
+        <v>405012</v>
       </c>
       <c r="G43">
-        <v>118531</v>
+        <v>420044</v>
       </c>
       <c r="H43">
-        <v>111210</v>
+        <v>464082</v>
       </c>
       <c r="I43">
-        <v>105269</v>
+        <v>472249</v>
       </c>
       <c r="J43">
-        <v>95575</v>
+        <v>469766</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2541,37 +2510,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cangaíba	13.495	34.742	65.638	97.792	115.070	137.442	136.623	141.172</t>
+          <t>Artur Alvim	11.045	25.962	35.773	44.551	80.000	105.155	101.455	102.502</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cangaíba</t>
+          <t>Artur Alvim</t>
         </is>
       </c>
       <c r="C44">
-        <v>13495</v>
+        <v>11045</v>
       </c>
       <c r="D44">
-        <v>34742</v>
+        <v>25962</v>
       </c>
       <c r="E44">
-        <v>65638</v>
+        <v>35773</v>
       </c>
       <c r="F44">
-        <v>97792</v>
+        <v>44551</v>
       </c>
       <c r="G44">
-        <v>115070</v>
+        <v>80000</v>
       </c>
       <c r="H44">
-        <v>137442</v>
+        <v>105155</v>
       </c>
       <c r="I44">
-        <v>136623</v>
+        <v>101455</v>
       </c>
       <c r="J44">
-        <v>141172</v>
+        <v>102502</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2592,37 +2561,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Penha	55.507	96.315	127.642	140.213	133.006	124.292	127.820	132.452</t>
+          <t>Cangaíba	11.045	25.962	88.423	110.121	122.044	151.488	136.623	138.868</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Penha</t>
+          <t>Cangaíba</t>
         </is>
       </c>
       <c r="C45">
-        <v>55507</v>
+        <v>11045</v>
       </c>
       <c r="D45">
-        <v>96315</v>
+        <v>25962</v>
       </c>
       <c r="E45">
-        <v>127642</v>
+        <v>88423</v>
       </c>
       <c r="F45">
-        <v>140213</v>
+        <v>110121</v>
       </c>
       <c r="G45">
-        <v>133006</v>
+        <v>122044</v>
       </c>
       <c r="H45">
-        <v>124292</v>
+        <v>151488</v>
       </c>
       <c r="I45">
-        <v>127820</v>
+        <v>136623</v>
       </c>
       <c r="J45">
-        <v>132452</v>
+        <v>138868</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2643,37 +2612,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Vila Matilde	19.465	40.010	74.363	117.530	109.023	102.935	104.947	103.558</t>
+          <t>Penha	58.236	136.883	163.535	203.664	124.000	118.720	127.885	127.562</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vila Matilde</t>
+          <t>Penha</t>
         </is>
       </c>
       <c r="C46">
-        <v>19465</v>
+        <v>58236</v>
       </c>
       <c r="D46">
-        <v>40010</v>
+        <v>136883</v>
       </c>
       <c r="E46">
-        <v>74363</v>
+        <v>163535</v>
       </c>
       <c r="F46">
-        <v>117530</v>
+        <v>203664</v>
       </c>
       <c r="G46">
-        <v>109023</v>
+        <v>124000</v>
       </c>
       <c r="H46">
-        <v>102935</v>
+        <v>118720</v>
       </c>
       <c r="I46">
-        <v>104947</v>
+        <v>127885</v>
       </c>
       <c r="J46">
-        <v>103558</v>
+        <v>127562</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2694,41 +2663,41 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Subprefeitura São Mateus	29.586	57.823	134.416	221.459	300.446	381.718	426.794	453.527</t>
+          <t>Vila Matilde	20.087	47.228	37.479	46.676	94.000	88.719	106.286	100.834</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Subprefeitura São Mateus</t>
+          <t>Vila Matilde</t>
         </is>
       </c>
       <c r="C47">
-        <v>29586</v>
+        <v>20087</v>
       </c>
       <c r="D47">
-        <v>57823</v>
+        <v>47228</v>
       </c>
       <c r="E47">
-        <v>134416</v>
+        <v>37479</v>
       </c>
       <c r="F47">
-        <v>221459</v>
+        <v>46676</v>
       </c>
       <c r="G47">
-        <v>300446</v>
+        <v>94000</v>
       </c>
       <c r="H47">
-        <v>381718</v>
+        <v>88719</v>
       </c>
       <c r="I47">
-        <v>426794</v>
+        <v>106286</v>
       </c>
       <c r="J47">
-        <v>453527</v>
+        <v>100834</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -2738,48 +2707,48 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Subprefeitura São Mateus</t>
+          <t>Subprefeitura Penha</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Iguatemi	1.695	3.882	15.620	32.595	59.820	101.780	127.662	149.700</t>
+          <t>Subprefeitura São Mateus	13.141	30.889	78.397	128.532	174.552	378.530	426.794	453.527</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Iguatemi</t>
+          <t>Subprefeitura São Mateus</t>
         </is>
       </c>
       <c r="C48">
-        <v>1695</v>
+        <v>13141</v>
       </c>
       <c r="D48">
-        <v>3882</v>
+        <v>30889</v>
       </c>
       <c r="E48">
-        <v>15620</v>
+        <v>78397</v>
       </c>
       <c r="F48">
-        <v>32595</v>
+        <v>128532</v>
       </c>
       <c r="G48">
-        <v>59820</v>
+        <v>174552</v>
       </c>
       <c r="H48">
-        <v>101780</v>
+        <v>378530</v>
       </c>
       <c r="I48">
-        <v>127662</v>
+        <v>426794</v>
       </c>
       <c r="J48">
-        <v>149700</v>
+        <v>453527</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -2796,37 +2765,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>São Mateus	25.106	47.833	86.045	118.421	150.764	154.850	155.140	155.682</t>
+          <t>Iguatemi	1.855	4.360	11.066	18.143	24.636	101.780	127.662	149.700</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>São Mateus</t>
+          <t>Iguatemi</t>
         </is>
       </c>
       <c r="C49">
-        <v>25106</v>
+        <v>1855</v>
       </c>
       <c r="D49">
-        <v>47833</v>
+        <v>4360</v>
       </c>
       <c r="E49">
-        <v>86045</v>
+        <v>11066</v>
       </c>
       <c r="F49">
-        <v>118421</v>
+        <v>18143</v>
       </c>
       <c r="G49">
-        <v>150764</v>
+        <v>24636</v>
       </c>
       <c r="H49">
-        <v>154850</v>
+        <v>101780</v>
       </c>
       <c r="I49">
-        <v>155140</v>
+        <v>127662</v>
       </c>
       <c r="J49">
-        <v>155682</v>
+        <v>149700</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2847,37 +2816,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>São Rafael	2.785	6.108	32.751	70.443	89.862	125.088	143.992	148.145</t>
+          <t>São Mateus	7.606	17.880	45.381	74.402	101.036	151.650	155.140	155.682</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>São Rafael</t>
+          <t>São Mateus</t>
         </is>
       </c>
       <c r="C50">
-        <v>2785</v>
+        <v>7606</v>
       </c>
       <c r="D50">
-        <v>6108</v>
+        <v>17880</v>
       </c>
       <c r="E50">
-        <v>32751</v>
+        <v>45381</v>
       </c>
       <c r="F50">
-        <v>70443</v>
+        <v>74402</v>
       </c>
       <c r="G50">
-        <v>89862</v>
+        <v>101036</v>
       </c>
       <c r="H50">
-        <v>125088</v>
+        <v>151650</v>
       </c>
       <c r="I50">
-        <v>143992</v>
+        <v>155140</v>
       </c>
       <c r="J50">
-        <v>148145</v>
+        <v>155682</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2898,41 +2867,41 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Subprefeitura São Miguel	12.063	40.456	138.085	260.942	322.581	378.944	370.100	344.609</t>
+          <t>São Rafael	3.680	8.649	21.950	35.987	48.880	125.100	143.992	148.145</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Subprefeitura São Miguel</t>
+          <t>São Rafael</t>
         </is>
       </c>
       <c r="C51">
-        <v>12063</v>
+        <v>3680</v>
       </c>
       <c r="D51">
-        <v>40456</v>
+        <v>8649</v>
       </c>
       <c r="E51">
-        <v>138085</v>
+        <v>21950</v>
       </c>
       <c r="F51">
-        <v>260942</v>
+        <v>35987</v>
       </c>
       <c r="G51">
-        <v>322581</v>
+        <v>48880</v>
       </c>
       <c r="H51">
-        <v>378944</v>
+        <v>125100</v>
       </c>
       <c r="I51">
-        <v>370100</v>
+        <v>143992</v>
       </c>
       <c r="J51">
-        <v>344609</v>
+        <v>148145</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -2942,48 +2911,48 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Subprefeitura São Miguel</t>
+          <t>Subprefeitura São Mateus</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jardim Helena	3.841	13.542	48.255	91.079	118.381	139.612	135.411	129.409</t>
+          <t>Subprefeitura São Miguel	11.082	26.049	66.024	108.246	246.391	371.493	370.100	344.609</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jardim Helena</t>
+          <t>Subprefeitura São Miguel</t>
         </is>
       </c>
       <c r="C52">
-        <v>3841</v>
+        <v>11082</v>
       </c>
       <c r="D52">
-        <v>13542</v>
+        <v>26049</v>
       </c>
       <c r="E52">
-        <v>48255</v>
+        <v>66024</v>
       </c>
       <c r="F52">
-        <v>91079</v>
+        <v>108246</v>
       </c>
       <c r="G52">
-        <v>118381</v>
+        <v>246391</v>
       </c>
       <c r="H52">
-        <v>139612</v>
+        <v>371493</v>
       </c>
       <c r="I52">
-        <v>135411</v>
+        <v>370100</v>
       </c>
       <c r="J52">
-        <v>129409</v>
+        <v>344609</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3000,37 +2969,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>São Miguel	4.008	12.052	49.859	100.182	102.964	99.072	92.081	81.011</t>
+          <t>Jardim Helena	2.651	6.232	15.795	25.897	59.000	139.612	135.411	129.409</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>São Miguel</t>
+          <t>Jardim Helena</t>
         </is>
       </c>
       <c r="C53">
-        <v>4008</v>
+        <v>2651</v>
       </c>
       <c r="D53">
-        <v>12052</v>
+        <v>6232</v>
       </c>
       <c r="E53">
-        <v>49859</v>
+        <v>15795</v>
       </c>
       <c r="F53">
-        <v>100182</v>
+        <v>25897</v>
       </c>
       <c r="G53">
-        <v>102964</v>
+        <v>59000</v>
       </c>
       <c r="H53">
-        <v>99072</v>
+        <v>139612</v>
       </c>
       <c r="I53">
-        <v>92081</v>
+        <v>135411</v>
       </c>
       <c r="J53">
-        <v>81011</v>
+        <v>129409</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3051,37 +3020,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Vila Jacuí	4.214	14.862	39.971	69.681	101.236	140.260	142.608	134.189</t>
+          <t>São Miguel	5.778	13.582	34.426	56.442	128.391	91.314	92.081	81.011</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vila Jacuí</t>
+          <t>São Miguel</t>
         </is>
       </c>
       <c r="C54">
-        <v>4214</v>
+        <v>5778</v>
       </c>
       <c r="D54">
-        <v>14862</v>
+        <v>13582</v>
       </c>
       <c r="E54">
-        <v>39971</v>
+        <v>34426</v>
       </c>
       <c r="F54">
-        <v>69681</v>
+        <v>56442</v>
       </c>
       <c r="G54">
-        <v>101236</v>
+        <v>128391</v>
       </c>
       <c r="H54">
-        <v>140260</v>
+        <v>91314</v>
       </c>
       <c r="I54">
-        <v>142608</v>
+        <v>92081</v>
       </c>
       <c r="J54">
-        <v>134189</v>
+        <v>81011</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3102,41 +3071,41 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Subprefeitura Sapopemba	20.806	44.326	107.192	178.989	257.617	282.239	284.524	266.715</t>
+          <t>Vila Jacuí	2.653	6.235	15.803	25.907	59.000	140.567	142.608	134.189</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Subprefeitura Sapopemba</t>
+          <t>Vila Jacuí</t>
         </is>
       </c>
       <c r="C55">
-        <v>20806</v>
+        <v>2653</v>
       </c>
       <c r="D55">
-        <v>44326</v>
+        <v>6235</v>
       </c>
       <c r="E55">
-        <v>107192</v>
+        <v>15803</v>
       </c>
       <c r="F55">
-        <v>178989</v>
+        <v>25907</v>
       </c>
       <c r="G55">
-        <v>257617</v>
+        <v>59000</v>
       </c>
       <c r="H55">
-        <v>282239</v>
+        <v>140567</v>
       </c>
       <c r="I55">
-        <v>284524</v>
+        <v>142608</v>
       </c>
       <c r="J55">
-        <v>266715</v>
+        <v>134189</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3146,35 +3115,35 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Subprefeitura Sapopemba</t>
+          <t>Subprefeitura São Miguel</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sapopemba	20.806	44.326	107.192	178.989	257.617	282.239	284.524	266.715</t>
+          <t>Subprefeitura Sapopemba	5.700	13.398	34.004	55.750	156.400	282.239	284.524	266.715</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sapopemba</t>
+          <t>Subprefeitura Sapopemba</t>
         </is>
       </c>
       <c r="C56">
-        <v>20806</v>
+        <v>5700</v>
       </c>
       <c r="D56">
-        <v>44326</v>
+        <v>13398</v>
       </c>
       <c r="E56">
-        <v>107192</v>
+        <v>34004</v>
       </c>
       <c r="F56">
-        <v>178989</v>
+        <v>55750</v>
       </c>
       <c r="G56">
-        <v>257617</v>
+        <v>156400</v>
       </c>
       <c r="H56">
         <v>282239</v>
@@ -3187,7 +3156,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3204,41 +3173,41 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Subprefeitura Vila Prudente	75.773	135.363	215.201	281.207	266.333	240.495	246.589	243.728</t>
+          <t>Sapopemba	5.700	13.398	34.004	55.750	156.400	282.239	284.524	266.715</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Subprefeitura Vila Prudente</t>
+          <t>Sapopemba</t>
         </is>
       </c>
       <c r="C57">
-        <v>75773</v>
+        <v>5700</v>
       </c>
       <c r="D57">
-        <v>135363</v>
+        <v>13398</v>
       </c>
       <c r="E57">
-        <v>215201</v>
+        <v>34004</v>
       </c>
       <c r="F57">
-        <v>281207</v>
+        <v>55750</v>
       </c>
       <c r="G57">
-        <v>266333</v>
+        <v>156400</v>
       </c>
       <c r="H57">
-        <v>240495</v>
+        <v>282239</v>
       </c>
       <c r="I57">
-        <v>246589</v>
+        <v>284524</v>
       </c>
       <c r="J57">
-        <v>243728</v>
+        <v>266715</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3248,48 +3217,48 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Subprefeitura Vila Prudente</t>
+          <t>Subprefeitura Sapopemba</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>São Lucas	29.536	62.557	113.504	156.430	152.036	138.391	142.347	138.038</t>
+          <t>Subprefeitura Vila Prudente	34.331	80.697	136.315	190.791	223.150	233.208	246.589	243.728</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>São Lucas</t>
+          <t>Subprefeitura Vila Prudente</t>
         </is>
       </c>
       <c r="C58">
-        <v>29536</v>
+        <v>34331</v>
       </c>
       <c r="D58">
-        <v>62557</v>
+        <v>80697</v>
       </c>
       <c r="E58">
-        <v>113504</v>
+        <v>136315</v>
       </c>
       <c r="F58">
-        <v>156430</v>
+        <v>190791</v>
       </c>
       <c r="G58">
-        <v>152036</v>
+        <v>223150</v>
       </c>
       <c r="H58">
-        <v>138391</v>
+        <v>233208</v>
       </c>
       <c r="I58">
-        <v>142347</v>
+        <v>246589</v>
       </c>
       <c r="J58">
-        <v>138038</v>
+        <v>243728</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3306,37 +3275,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Vila Prudente	46.237	72.806	101.697	124.777	114.297	102.104	104.242	105.690</t>
+          <t>São Lucas	15.792	37.121	62.705	87.764	102.650	131.050	142.347	138.038</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Vila Prudente</t>
+          <t>São Lucas</t>
         </is>
       </c>
       <c r="C59">
-        <v>46237</v>
+        <v>15792</v>
       </c>
       <c r="D59">
-        <v>72806</v>
+        <v>37121</v>
       </c>
       <c r="E59">
-        <v>101697</v>
+        <v>62705</v>
       </c>
       <c r="F59">
-        <v>124777</v>
+        <v>87764</v>
       </c>
       <c r="G59">
-        <v>114297</v>
+        <v>102650</v>
       </c>
       <c r="H59">
-        <v>102104</v>
+        <v>131050</v>
       </c>
       <c r="I59">
-        <v>104242</v>
+        <v>142347</v>
       </c>
       <c r="J59">
-        <v>105690</v>
+        <v>138038</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3357,46 +3326,46 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Região Norte	365.783	800.191	1.360.504	1.788.421	1.947.435	2.092.360	2.214.654	2.208.963</t>
+          <t>Vila Prudente	18.539	43.576	73.610	103.027	120.500	102.158	104.242	105.690</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Região Norte</t>
+          <t>Vila Prudente</t>
         </is>
       </c>
       <c r="C60">
-        <v>365783</v>
+        <v>18539</v>
       </c>
       <c r="D60">
-        <v>800191</v>
+        <v>43576</v>
       </c>
       <c r="E60">
-        <v>1360504</v>
+        <v>73610</v>
       </c>
       <c r="F60">
-        <v>1788421</v>
+        <v>103027</v>
       </c>
       <c r="G60">
-        <v>1947435</v>
+        <v>120500</v>
       </c>
       <c r="H60">
-        <v>2092360</v>
+        <v>102158</v>
       </c>
       <c r="I60">
-        <v>2214654</v>
+        <v>104242</v>
       </c>
       <c r="J60">
-        <v>2208963</v>
+        <v>105690</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Região</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Região Norte</t>
+          <t>Região Leste</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -3408,41 +3377,41 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Subprefeitura Casa Verde-Cachoeirinha	98.662	179.683	252.352	298.092	312.670	314.170	309.376	306.275</t>
+          <t>Região Norte	485.456	886.945	1.360.504	1.788.421	1.947.435	2.092.360	2.214.654	2.208.963</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Subprefeitura Casa Verde-Cachoeirinha</t>
+          <t>Região Norte</t>
         </is>
       </c>
       <c r="C61">
-        <v>98662</v>
+        <v>485456</v>
       </c>
       <c r="D61">
-        <v>179683</v>
+        <v>886945</v>
       </c>
       <c r="E61">
-        <v>252352</v>
+        <v>1360504</v>
       </c>
       <c r="F61">
-        <v>298092</v>
+        <v>1788421</v>
       </c>
       <c r="G61">
-        <v>312670</v>
+        <v>1947435</v>
       </c>
       <c r="H61">
-        <v>314170</v>
+        <v>2092360</v>
       </c>
       <c r="I61">
-        <v>309376</v>
+        <v>2214654</v>
       </c>
       <c r="J61">
-        <v>306275</v>
+        <v>2208963</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Região</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -3452,48 +3421,48 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Subprefeitura Casa Verde-Cachoeirinha</t>
+          <t>Subprefeitura Vila Prudente</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cachoeirinha	32.461	58.831	85.048	105.726	125.852	148.496	143.523	143.366</t>
+          <t>Subprefeitura Casa Verde-Cachoeirinha	116.510	168.519	252.352	298.092	312.670	314.170	309.376	306.275</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cachoeirinha</t>
+          <t>Subprefeitura Casa Verde-Cachoeirinha</t>
         </is>
       </c>
       <c r="C62">
-        <v>32461</v>
+        <v>116510</v>
       </c>
       <c r="D62">
-        <v>58831</v>
+        <v>168519</v>
       </c>
       <c r="E62">
-        <v>85048</v>
+        <v>252352</v>
       </c>
       <c r="F62">
-        <v>105726</v>
+        <v>298092</v>
       </c>
       <c r="G62">
-        <v>125852</v>
+        <v>312670</v>
       </c>
       <c r="H62">
-        <v>148496</v>
+        <v>314170</v>
       </c>
       <c r="I62">
-        <v>143523</v>
+        <v>309376</v>
       </c>
       <c r="J62">
-        <v>143366</v>
+        <v>306275</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -3510,37 +3479,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Casa Verde	43.371	74.349	92.722	103.455	96.396	83.629	85.624	80.536</t>
+          <t>Cachoeirinha	41.250	59.663	85.048	105.726	125.852	148.496	143.523	143.366</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Casa Verde</t>
+          <t>Cachoeirinha</t>
         </is>
       </c>
       <c r="C63">
-        <v>43371</v>
+        <v>41250</v>
       </c>
       <c r="D63">
-        <v>74349</v>
+        <v>59663</v>
       </c>
       <c r="E63">
-        <v>92722</v>
+        <v>85048</v>
       </c>
       <c r="F63">
-        <v>103455</v>
+        <v>105726</v>
       </c>
       <c r="G63">
-        <v>96396</v>
+        <v>125852</v>
       </c>
       <c r="H63">
-        <v>83629</v>
+        <v>148496</v>
       </c>
       <c r="I63">
-        <v>85624</v>
+        <v>143523</v>
       </c>
       <c r="J63">
-        <v>80536</v>
+        <v>143366</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -3561,37 +3530,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Limão	22.830	46.503	74.582	88.911	90.422	82.045	80.229	82.373</t>
+          <t>Casa Verde	54.215	78.411	92.722	103.455	96.396	83.629	85.624	80.536</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Limão</t>
+          <t>Casa Verde</t>
         </is>
       </c>
       <c r="C64">
-        <v>22830</v>
+        <v>54215</v>
       </c>
       <c r="D64">
-        <v>46503</v>
+        <v>78411</v>
       </c>
       <c r="E64">
-        <v>74582</v>
+        <v>92722</v>
       </c>
       <c r="F64">
-        <v>88911</v>
+        <v>103455</v>
       </c>
       <c r="G64">
-        <v>90422</v>
+        <v>96396</v>
       </c>
       <c r="H64">
-        <v>82045</v>
+        <v>83629</v>
       </c>
       <c r="I64">
-        <v>80229</v>
+        <v>85624</v>
       </c>
       <c r="J64">
-        <v>82373</v>
+        <v>80536</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -3612,41 +3581,41 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Subprefeitura Freguesia-Brasilândia	36.816	94.745	218.763	317.019	354.263	391.404	407.245	380.513</t>
+          <t>Limão	21.045	30.445	74.582	88.911	90.422	82.045	80.229	82.373</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Subprefeitura Freguesia-Brasilândia</t>
+          <t>Limão</t>
         </is>
       </c>
       <c r="C65">
-        <v>36816</v>
+        <v>21045</v>
       </c>
       <c r="D65">
-        <v>94745</v>
+        <v>30445</v>
       </c>
       <c r="E65">
-        <v>218763</v>
+        <v>74582</v>
       </c>
       <c r="F65">
-        <v>317019</v>
+        <v>88911</v>
       </c>
       <c r="G65">
-        <v>354263</v>
+        <v>90422</v>
       </c>
       <c r="H65">
-        <v>391404</v>
+        <v>82045</v>
       </c>
       <c r="I65">
-        <v>407245</v>
+        <v>80229</v>
       </c>
       <c r="J65">
-        <v>380513</v>
+        <v>82373</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -3656,48 +3625,48 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Subprefeitura Freguesia-Brasilândia</t>
+          <t>Subprefeitura Casa Verde-Cachoeirinha</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Brasilândia	19.329	49.743	114.855	166.441	201.591	246.481	264.918	243.273</t>
+          <t>Subprefeitura Freguesia-Brasilândia	100.225	151.782	218.763	317.019	354.263	391.404	407.245	380.513</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Brasilândia</t>
+          <t>Subprefeitura Freguesia-Brasilândia</t>
         </is>
       </c>
       <c r="C66">
-        <v>19329</v>
+        <v>100225</v>
       </c>
       <c r="D66">
-        <v>49743</v>
+        <v>151782</v>
       </c>
       <c r="E66">
-        <v>114855</v>
+        <v>218763</v>
       </c>
       <c r="F66">
-        <v>166441</v>
+        <v>317019</v>
       </c>
       <c r="G66">
-        <v>201591</v>
+        <v>354263</v>
       </c>
       <c r="H66">
-        <v>246481</v>
+        <v>391404</v>
       </c>
       <c r="I66">
-        <v>264918</v>
+        <v>407245</v>
       </c>
       <c r="J66">
-        <v>243273</v>
+        <v>380513</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -3714,37 +3683,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Freguesia do Ó	17.487	45.002	103.908	150.578	152.672	144.923	142.327	137.240</t>
+          <t>Brasilândia	52.650	79.734	114.855	166.441	201.591	246.481	264.918	243.273</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Freguesia do Ó</t>
+          <t>Brasilândia</t>
         </is>
       </c>
       <c r="C67">
-        <v>17487</v>
+        <v>52650</v>
       </c>
       <c r="D67">
-        <v>45002</v>
+        <v>79734</v>
       </c>
       <c r="E67">
-        <v>103908</v>
+        <v>114855</v>
       </c>
       <c r="F67">
-        <v>150578</v>
+        <v>166441</v>
       </c>
       <c r="G67">
-        <v>152672</v>
+        <v>201591</v>
       </c>
       <c r="H67">
-        <v>144923</v>
+        <v>246481</v>
       </c>
       <c r="I67">
-        <v>142327</v>
+        <v>264918</v>
       </c>
       <c r="J67">
-        <v>137240</v>
+        <v>243273</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -3765,41 +3734,41 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Subprefeitura Jaçanã-Tremembé	35.112	85.556	137.607	176.895	211.905	255.612	291.867	283.892</t>
+          <t>Freguesia do Ó	47.575	72.048	103.908	150.578	152.672	144.923	142.327	137.240</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Subprefeitura Jaçanã-Tremembé</t>
+          <t>Freguesia do Ó</t>
         </is>
       </c>
       <c r="C68">
-        <v>35112</v>
+        <v>47575</v>
       </c>
       <c r="D68">
-        <v>85556</v>
+        <v>72048</v>
       </c>
       <c r="E68">
-        <v>137607</v>
+        <v>103908</v>
       </c>
       <c r="F68">
-        <v>176895</v>
+        <v>150578</v>
       </c>
       <c r="G68">
-        <v>211905</v>
+        <v>152672</v>
       </c>
       <c r="H68">
-        <v>255612</v>
+        <v>144923</v>
       </c>
       <c r="I68">
-        <v>291867</v>
+        <v>142327</v>
       </c>
       <c r="J68">
-        <v>283892</v>
+        <v>137240</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -3809,48 +3778,48 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Subprefeitura Jaçanã-Tremembé</t>
+          <t>Subprefeitura Freguesia-Brasilândia</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Jaçanã	15.895	38.731	62.294	80.080	86.830	92.380	93.186	87.329</t>
+          <t>Subprefeitura Jaçanã-Tremembé	63.090	90.582	137.607	176.895	211.905	255.612	291.867	283.892</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jaçanã</t>
+          <t>Subprefeitura Jaçanã-Tremembé</t>
         </is>
       </c>
       <c r="C69">
-        <v>15895</v>
+        <v>63090</v>
       </c>
       <c r="D69">
-        <v>38731</v>
+        <v>90582</v>
       </c>
       <c r="E69">
-        <v>62294</v>
+        <v>137607</v>
       </c>
       <c r="F69">
-        <v>80080</v>
+        <v>176895</v>
       </c>
       <c r="G69">
-        <v>86830</v>
+        <v>211905</v>
       </c>
       <c r="H69">
-        <v>92380</v>
+        <v>255612</v>
       </c>
       <c r="I69">
-        <v>93186</v>
+        <v>291867</v>
       </c>
       <c r="J69">
-        <v>87329</v>
+        <v>283892</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -3867,37 +3836,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Tremembé	19.217	46.825	75.313	96.815	125.075	163.232	198.681	196.563</t>
+          <t>Jaçanã	28.560	41.004	62.294	80.080	86.830	92.380	93.186	87.329</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tremembé</t>
+          <t>Jaçanã</t>
         </is>
       </c>
       <c r="C70">
-        <v>19217</v>
+        <v>28560</v>
       </c>
       <c r="D70">
-        <v>46825</v>
+        <v>41004</v>
       </c>
       <c r="E70">
-        <v>75313</v>
+        <v>62294</v>
       </c>
       <c r="F70">
-        <v>96815</v>
+        <v>80080</v>
       </c>
       <c r="G70">
-        <v>125075</v>
+        <v>86830</v>
       </c>
       <c r="H70">
-        <v>163232</v>
+        <v>92380</v>
       </c>
       <c r="I70">
-        <v>198681</v>
+        <v>93186</v>
       </c>
       <c r="J70">
-        <v>196563</v>
+        <v>87329</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -3918,41 +3887,41 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Subprefeitura Perus	4.792	7.985	23.441	41.546	58.709	109.116	146.046	163.083</t>
+          <t>Tremembé	34.530	49.578	75.313	96.815	125.075	163.232	198.681	196.563</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Subprefeitura Perus</t>
+          <t>Tremembé</t>
         </is>
       </c>
       <c r="C71">
-        <v>4792</v>
+        <v>34530</v>
       </c>
       <c r="D71">
-        <v>7985</v>
+        <v>49578</v>
       </c>
       <c r="E71">
-        <v>23441</v>
+        <v>75313</v>
       </c>
       <c r="F71">
-        <v>41546</v>
+        <v>96815</v>
       </c>
       <c r="G71">
-        <v>58709</v>
+        <v>125075</v>
       </c>
       <c r="H71">
-        <v>109116</v>
+        <v>163232</v>
       </c>
       <c r="I71">
-        <v>146046</v>
+        <v>198681</v>
       </c>
       <c r="J71">
-        <v>163083</v>
+        <v>196563</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -3962,48 +3931,48 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Subprefeitura Perus</t>
+          <t>Subprefeitura Jaçanã-Tremembé</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Anhanguera	429	1.030	2.626	5.350	12.408	38.427	65.859	75.360</t>
+          <t>Subprefeitura Perus-Anhangüera	10.750	15.627	23.441	41.546	58.709	109.116	146.046	163.083</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Anhanguera</t>
+          <t>Subprefeitura Perus-Anhangüera</t>
         </is>
       </c>
       <c r="C72">
-        <v>429</v>
+        <v>10750</v>
       </c>
       <c r="D72">
-        <v>1030</v>
+        <v>15627</v>
       </c>
       <c r="E72">
-        <v>2626</v>
+        <v>23441</v>
       </c>
       <c r="F72">
-        <v>5350</v>
+        <v>41546</v>
       </c>
       <c r="G72">
-        <v>12408</v>
+        <v>58709</v>
       </c>
       <c r="H72">
-        <v>38427</v>
+        <v>109116</v>
       </c>
       <c r="I72">
-        <v>65859</v>
+        <v>146046</v>
       </c>
       <c r="J72">
-        <v>75360</v>
+        <v>163083</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4013,44 +3982,44 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Subprefeitura Perus</t>
+          <t>Subprefeitura Perus-Anhangüera</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Perus	4.363	6.955	20.815	36.196	46.301	70.689	80.187	87.723</t>
+          <t>Anhangüera	1.250	1.817	2.626	5.350	12.408	38.427	65.859	75.360</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Perus</t>
+          <t>Anhangüera</t>
         </is>
       </c>
       <c r="C73">
-        <v>4363</v>
+        <v>1250</v>
       </c>
       <c r="D73">
-        <v>6955</v>
+        <v>1817</v>
       </c>
       <c r="E73">
-        <v>20815</v>
+        <v>2626</v>
       </c>
       <c r="F73">
-        <v>36196</v>
+        <v>5350</v>
       </c>
       <c r="G73">
-        <v>46301</v>
+        <v>12408</v>
       </c>
       <c r="H73">
-        <v>70689</v>
+        <v>38427</v>
       </c>
       <c r="I73">
-        <v>80187</v>
+        <v>65859</v>
       </c>
       <c r="J73">
-        <v>87723</v>
+        <v>75360</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -4064,48 +4033,48 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Subprefeitura Perus</t>
+          <t>Subprefeitura Perus-Anhangüera</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Subprefeitura Pirituba-Jaraguá	31.505	84.232	176.696	249.552	315.876	390.530	437.592	480.218</t>
+          <t>Perus	9.500	13.810	20.815	36.196	46.301	70.689	80.187	87.723</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Subprefeitura Pirituba-Jaraguá</t>
+          <t>Perus</t>
         </is>
       </c>
       <c r="C74">
-        <v>31505</v>
+        <v>9500</v>
       </c>
       <c r="D74">
-        <v>84232</v>
+        <v>13810</v>
       </c>
       <c r="E74">
-        <v>176696</v>
+        <v>20815</v>
       </c>
       <c r="F74">
-        <v>249552</v>
+        <v>36196</v>
       </c>
       <c r="G74">
-        <v>315876</v>
+        <v>46301</v>
       </c>
       <c r="H74">
-        <v>390530</v>
+        <v>70689</v>
       </c>
       <c r="I74">
-        <v>437592</v>
+        <v>80187</v>
       </c>
       <c r="J74">
-        <v>480218</v>
+        <v>87723</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4115,48 +4084,48 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Subprefeitura Pirituba-Jaraguá</t>
+          <t>Subprefeitura Perus-Anhangüera</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Jaraguá	5.098	12.970	29.531	47.416	93.185	145.900	184.818	211.610</t>
+          <t>Subprefeitura Pirituba-Jaraguá	81.045	116.510	176.696	249.552	315.876	390.530	437.592	480.218</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Jaraguá</t>
+          <t>Subprefeitura Pirituba-Jaraguá</t>
         </is>
       </c>
       <c r="C75">
-        <v>5098</v>
+        <v>81045</v>
       </c>
       <c r="D75">
-        <v>12970</v>
+        <v>116510</v>
       </c>
       <c r="E75">
-        <v>29531</v>
+        <v>176696</v>
       </c>
       <c r="F75">
-        <v>47416</v>
+        <v>249552</v>
       </c>
       <c r="G75">
-        <v>93185</v>
+        <v>315876</v>
       </c>
       <c r="H75">
-        <v>145900</v>
+        <v>390530</v>
       </c>
       <c r="I75">
-        <v>184818</v>
+        <v>437592</v>
       </c>
       <c r="J75">
-        <v>211610</v>
+        <v>480218</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -4173,37 +4142,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Pirituba	16.218	43.682	96.397	132.679	152.305	161.796	167.931	179.724</t>
+          <t>Jaraguá	13.542	19.467	29.531	47.416	93.185	145.900	184.818	211.610</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Pirituba</t>
+          <t>Jaraguá</t>
         </is>
       </c>
       <c r="C76">
-        <v>16218</v>
+        <v>13542</v>
       </c>
       <c r="D76">
-        <v>43682</v>
+        <v>19467</v>
       </c>
       <c r="E76">
-        <v>96397</v>
+        <v>29531</v>
       </c>
       <c r="F76">
-        <v>132679</v>
+        <v>47416</v>
       </c>
       <c r="G76">
-        <v>152305</v>
+        <v>93185</v>
       </c>
       <c r="H76">
-        <v>161796</v>
+        <v>145900</v>
       </c>
       <c r="I76">
-        <v>167931</v>
+        <v>184818</v>
       </c>
       <c r="J76">
-        <v>179724</v>
+        <v>211610</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -4224,37 +4193,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>São Domingos	10.189	27.580	50.768	69.457	70.386	82.834	84.843	88.884</t>
+          <t>Pirituba	44.201	63.544	96.397	132.679	152.305	161.796	167.931	179.724</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>São Domingos</t>
+          <t>Pirituba</t>
         </is>
       </c>
       <c r="C77">
-        <v>10189</v>
+        <v>44201</v>
       </c>
       <c r="D77">
-        <v>27580</v>
+        <v>63544</v>
       </c>
       <c r="E77">
-        <v>50768</v>
+        <v>96397</v>
       </c>
       <c r="F77">
-        <v>69457</v>
+        <v>132679</v>
       </c>
       <c r="G77">
-        <v>70386</v>
+        <v>152305</v>
       </c>
       <c r="H77">
-        <v>82834</v>
+        <v>161796</v>
       </c>
       <c r="I77">
-        <v>84843</v>
+        <v>167931</v>
       </c>
       <c r="J77">
-        <v>88884</v>
+        <v>179724</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -4275,41 +4244,41 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Subprefeitura Santana-Tucuruvi	79.287	165.319	264.715	342.815	353.585	327.135	324.815	318.913</t>
+          <t>São Domingos	23.302	33.499	50.768	69.457	70.386	82.834	84.843	88.884</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Subprefeitura Santana-Tucuruvi</t>
+          <t>São Domingos</t>
         </is>
       </c>
       <c r="C78">
-        <v>79287</v>
+        <v>23302</v>
       </c>
       <c r="D78">
-        <v>165319</v>
+        <v>33499</v>
       </c>
       <c r="E78">
-        <v>264715</v>
+        <v>50768</v>
       </c>
       <c r="F78">
-        <v>342815</v>
+        <v>69457</v>
       </c>
       <c r="G78">
-        <v>353585</v>
+        <v>70386</v>
       </c>
       <c r="H78">
-        <v>327135</v>
+        <v>82834</v>
       </c>
       <c r="I78">
-        <v>324815</v>
+        <v>84843</v>
       </c>
       <c r="J78">
-        <v>318913</v>
+        <v>88884</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -4319,48 +4288,48 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Subprefeitura Santana-Tucuruvi</t>
+          <t>Subprefeitura Pirituba-Jaraguá</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mandaqui	19.130	41.256	66.911	88.203	104.022	103.113	107.580	103.665</t>
+          <t>Subprefeitura Santana-Tucuruvi	54.560	182.134	264.715	342.815	353.585	327.135	324.815	318.913</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mandaqui</t>
+          <t>Subprefeitura Santana-Tucuruvi</t>
         </is>
       </c>
       <c r="C79">
-        <v>19130</v>
+        <v>54560</v>
       </c>
       <c r="D79">
-        <v>41256</v>
+        <v>182134</v>
       </c>
       <c r="E79">
-        <v>66911</v>
+        <v>264715</v>
       </c>
       <c r="F79">
-        <v>88203</v>
+        <v>342815</v>
       </c>
       <c r="G79">
-        <v>104022</v>
+        <v>353585</v>
       </c>
       <c r="H79">
-        <v>103113</v>
+        <v>327135</v>
       </c>
       <c r="I79">
-        <v>107580</v>
+        <v>324815</v>
       </c>
       <c r="J79">
-        <v>103665</v>
+        <v>318913</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -4377,37 +4346,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Santana	35.087	69.999	110.120	139.026	137.679	124.654	118.797	115.689</t>
+          <t>Mandaqui	13.794	46.047	66.911	88.203	104.022	103.113	107.580	103.665</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Santana</t>
+          <t>Mandaqui</t>
         </is>
       </c>
       <c r="C80">
-        <v>35087</v>
+        <v>13794</v>
       </c>
       <c r="D80">
-        <v>69999</v>
+        <v>46047</v>
       </c>
       <c r="E80">
-        <v>110120</v>
+        <v>66911</v>
       </c>
       <c r="F80">
-        <v>139026</v>
+        <v>88203</v>
       </c>
       <c r="G80">
-        <v>137679</v>
+        <v>104022</v>
       </c>
       <c r="H80">
-        <v>124654</v>
+        <v>103113</v>
       </c>
       <c r="I80">
-        <v>118797</v>
+        <v>107580</v>
       </c>
       <c r="J80">
-        <v>115689</v>
+        <v>103665</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -4428,37 +4397,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Tucuruvi	25.070	54.064	87.684	115.586	111.884	99.368	98.438	99.559</t>
+          <t>Santana	22.706	75.794	110.120	139.026	137.679	124.654	118.797	115.689</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tucuruvi</t>
+          <t>Santana</t>
         </is>
       </c>
       <c r="C81">
-        <v>25070</v>
+        <v>22706</v>
       </c>
       <c r="D81">
-        <v>54064</v>
+        <v>75794</v>
       </c>
       <c r="E81">
-        <v>87684</v>
+        <v>110120</v>
       </c>
       <c r="F81">
-        <v>115586</v>
+        <v>139026</v>
       </c>
       <c r="G81">
-        <v>111884</v>
+        <v>137679</v>
       </c>
       <c r="H81">
-        <v>99368</v>
+        <v>124654</v>
       </c>
       <c r="I81">
-        <v>98438</v>
+        <v>118797</v>
       </c>
       <c r="J81">
-        <v>99559</v>
+        <v>115689</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -4479,41 +4448,41 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Subprefeitura Vila Maria-Vila Guilherme	79.609	182.671	286.930	362.502	340.427	304.393	297.713	276.069</t>
+          <t>Tucuruvi	18.060	60.293	87.684	115.586	111.884	99.368	98.438	99.559</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Subprefeitura Vila Maria-Vila Guilherme</t>
+          <t>Tucuruvi</t>
         </is>
       </c>
       <c r="C82">
-        <v>79609</v>
+        <v>18060</v>
       </c>
       <c r="D82">
-        <v>182671</v>
+        <v>60293</v>
       </c>
       <c r="E82">
-        <v>286930</v>
+        <v>87684</v>
       </c>
       <c r="F82">
-        <v>362502</v>
+        <v>115586</v>
       </c>
       <c r="G82">
-        <v>340427</v>
+        <v>111884</v>
       </c>
       <c r="H82">
-        <v>304393</v>
+        <v>99368</v>
       </c>
       <c r="I82">
-        <v>297713</v>
+        <v>98438</v>
       </c>
       <c r="J82">
-        <v>276069</v>
+        <v>99559</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -4523,48 +4492,48 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Subprefeitura Vila Maria-Vila Guilherme</t>
+          <t>Subprefeitura Santana-Tucuruvi</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Vila Guilherme	15.079	33.603	55.021	68.410	61.625	49.984	54.331	52.587</t>
+          <t>Subprefeitura Vila Maria-Vila Guilherme	59.276	161.791	286.930	362.502	340.427	304.393	297.713	276.069</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Vila Guilherme</t>
+          <t>Subprefeitura Vila Maria-Vila Guilherme</t>
         </is>
       </c>
       <c r="C83">
-        <v>15079</v>
+        <v>59276</v>
       </c>
       <c r="D83">
-        <v>33603</v>
+        <v>161791</v>
       </c>
       <c r="E83">
-        <v>55021</v>
+        <v>286930</v>
       </c>
       <c r="F83">
-        <v>68410</v>
+        <v>362502</v>
       </c>
       <c r="G83">
-        <v>61625</v>
+        <v>340427</v>
       </c>
       <c r="H83">
-        <v>49984</v>
+        <v>304393</v>
       </c>
       <c r="I83">
-        <v>54331</v>
+        <v>297713</v>
       </c>
       <c r="J83">
-        <v>52587</v>
+        <v>276069</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -4581,37 +4550,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Vila Maria	32.371	70.711	105.879	132.081	122.662	113.845	113.463	108.543</t>
+          <t>Vila Guilherme	11.373	31.042	55.021	68.410	61.625	49.984	54.331	52.587</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Vila Maria</t>
+          <t>Vila Guilherme</t>
         </is>
       </c>
       <c r="C84">
-        <v>32371</v>
+        <v>11373</v>
       </c>
       <c r="D84">
-        <v>70711</v>
+        <v>31042</v>
       </c>
       <c r="E84">
-        <v>105879</v>
+        <v>55021</v>
       </c>
       <c r="F84">
-        <v>132081</v>
+        <v>68410</v>
       </c>
       <c r="G84">
-        <v>122662</v>
+        <v>61625</v>
       </c>
       <c r="H84">
-        <v>113845</v>
+        <v>49984</v>
       </c>
       <c r="I84">
-        <v>113463</v>
+        <v>54331</v>
       </c>
       <c r="J84">
-        <v>108543</v>
+        <v>52587</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -4632,37 +4601,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Vila Medeiros	32.159	78.357	126.030	162.011	156.140	140.564	129.919	114.939</t>
+          <t>Vila Maria	21.875	59.712	105.879	132.081	122.662	113.845	113.463	108.543</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Vila Medeiros</t>
+          <t>Vila Maria</t>
         </is>
       </c>
       <c r="C85">
-        <v>32159</v>
+        <v>21875</v>
       </c>
       <c r="D85">
-        <v>78357</v>
+        <v>59712</v>
       </c>
       <c r="E85">
-        <v>126030</v>
+        <v>105879</v>
       </c>
       <c r="F85">
-        <v>162011</v>
+        <v>132081</v>
       </c>
       <c r="G85">
-        <v>156140</v>
+        <v>122662</v>
       </c>
       <c r="H85">
-        <v>140564</v>
+        <v>113845</v>
       </c>
       <c r="I85">
-        <v>129919</v>
+        <v>113463</v>
       </c>
       <c r="J85">
-        <v>114939</v>
+        <v>108543</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -4683,46 +4652,46 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Região Oeste	355.407	519.817	711.715	983.455	1.002.489	920.806	1.023.486	1.092.684</t>
+          <t>Vila Medeiros	26.028	71.037	126.030	162.011	156.140	140.564	129.919	114.939</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Região Oeste</t>
+          <t>Vila Medeiros</t>
         </is>
       </c>
       <c r="C86">
-        <v>355407</v>
+        <v>26028</v>
       </c>
       <c r="D86">
-        <v>519817</v>
+        <v>71037</v>
       </c>
       <c r="E86">
-        <v>711715</v>
+        <v>126030</v>
       </c>
       <c r="F86">
-        <v>983455</v>
+        <v>162011</v>
       </c>
       <c r="G86">
-        <v>1002489</v>
+        <v>156140</v>
       </c>
       <c r="H86">
-        <v>920806</v>
+        <v>140564</v>
       </c>
       <c r="I86">
-        <v>1023486</v>
+        <v>129919</v>
       </c>
       <c r="J86">
-        <v>1092684</v>
+        <v>114939</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Região</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Região Oeste</t>
+          <t>Região Norte</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -4734,41 +4703,41 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Subprefeitura Butantã	24.372	60.628	156.692	285.032	366.737	377.576	428.217	468.522</t>
+          <t>Região Oeste	355.407	519.817	711.715	983.455	1.002.489	920.806	1.023.486	1.092.684</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Subprefeitura Butantã</t>
+          <t>Região Oeste</t>
         </is>
       </c>
       <c r="C87">
-        <v>24372</v>
+        <v>355407</v>
       </c>
       <c r="D87">
-        <v>60628</v>
+        <v>519817</v>
       </c>
       <c r="E87">
-        <v>156692</v>
+        <v>711715</v>
       </c>
       <c r="F87">
-        <v>285032</v>
+        <v>983455</v>
       </c>
       <c r="G87">
-        <v>366737</v>
+        <v>1002489</v>
       </c>
       <c r="H87">
-        <v>377576</v>
+        <v>920806</v>
       </c>
       <c r="I87">
-        <v>428217</v>
+        <v>1023486</v>
       </c>
       <c r="J87">
-        <v>468522</v>
+        <v>1092684</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Região</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -4778,48 +4747,48 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Subprefeitura Butantã</t>
+          <t>Subprefeitura Vila Maria-Vila Guilherme</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Butantã	5.126	12.329	31.532	56.934	58.019	52.649	55.293	51.715</t>
+          <t>Subprefeitura Butantã	78.232	114.416	156.692	285.032	366.737	377.576	428.217	468.522</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Butantã</t>
+          <t>Subprefeitura Butantã</t>
         </is>
       </c>
       <c r="C88">
-        <v>5126</v>
+        <v>78232</v>
       </c>
       <c r="D88">
-        <v>12329</v>
+        <v>114416</v>
       </c>
       <c r="E88">
-        <v>31532</v>
+        <v>156692</v>
       </c>
       <c r="F88">
-        <v>56934</v>
+        <v>285032</v>
       </c>
       <c r="G88">
-        <v>58019</v>
+        <v>366737</v>
       </c>
       <c r="H88">
-        <v>52649</v>
+        <v>377576</v>
       </c>
       <c r="I88">
-        <v>55293</v>
+        <v>428217</v>
       </c>
       <c r="J88">
-        <v>51715</v>
+        <v>468522</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -4836,37 +4805,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Morumbi	3.121	8.902	18.724	31.077	40.031	34.588	46.957	43.690</t>
+          <t>Butantã	15.748	23.033	31.532	56.934	58.019	52.649	55.293	51.715</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Morumbi</t>
+          <t>Butantã</t>
         </is>
       </c>
       <c r="C89">
-        <v>3121</v>
+        <v>15748</v>
       </c>
       <c r="D89">
-        <v>8902</v>
+        <v>23033</v>
       </c>
       <c r="E89">
-        <v>18724</v>
+        <v>31532</v>
       </c>
       <c r="F89">
-        <v>31077</v>
+        <v>56934</v>
       </c>
       <c r="G89">
-        <v>40031</v>
+        <v>58019</v>
       </c>
       <c r="H89">
-        <v>34588</v>
+        <v>52649</v>
       </c>
       <c r="I89">
-        <v>46957</v>
+        <v>55293</v>
       </c>
       <c r="J89">
-        <v>43690</v>
+        <v>51715</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -4887,37 +4856,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Raposo Tavares	4.445	10.691	27.343	49.370	82.890	91.204	100.164	117.738</t>
+          <t>Morumbi	9.351	13.676	18.724	31.077	40.031	34.588	46.957	43.690</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Raposo Tavares</t>
+          <t>Morumbi</t>
         </is>
       </c>
       <c r="C90">
-        <v>4445</v>
+        <v>9351</v>
       </c>
       <c r="D90">
-        <v>10691</v>
+        <v>13676</v>
       </c>
       <c r="E90">
-        <v>27343</v>
+        <v>18724</v>
       </c>
       <c r="F90">
-        <v>49370</v>
+        <v>31077</v>
       </c>
       <c r="G90">
-        <v>82890</v>
+        <v>40031</v>
       </c>
       <c r="H90">
-        <v>91204</v>
+        <v>34588</v>
       </c>
       <c r="I90">
-        <v>100164</v>
+        <v>46957</v>
       </c>
       <c r="J90">
-        <v>117738</v>
+        <v>43690</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -4938,37 +4907,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Rio Pequeno	7.636	18.364	46.964	84.798	102.791	111.756	117.362	131.631</t>
+          <t>Raposo Tavares	13.654	19.969	27.343	49.370	82.890	91.204	100.164	117.738</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Rio Pequeno</t>
+          <t>Raposo Tavares</t>
         </is>
       </c>
       <c r="C91">
-        <v>7636</v>
+        <v>13654</v>
       </c>
       <c r="D91">
-        <v>18364</v>
+        <v>19969</v>
       </c>
       <c r="E91">
-        <v>46964</v>
+        <v>27343</v>
       </c>
       <c r="F91">
-        <v>84798</v>
+        <v>49370</v>
       </c>
       <c r="G91">
-        <v>102791</v>
+        <v>82890</v>
       </c>
       <c r="H91">
-        <v>111756</v>
+        <v>91204</v>
       </c>
       <c r="I91">
-        <v>117362</v>
+        <v>100164</v>
       </c>
       <c r="J91">
-        <v>131631</v>
+        <v>117738</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -4989,37 +4958,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Vila Sônia	4.044	10.342	32.129	62.853	83.006	87.379	108.441	123.748</t>
+          <t>Rio Pequeno	23.451	34.298	46.964	84.798	102.791	111.756	117.362	131.631</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Vila Sônia</t>
+          <t>Rio Pequeno</t>
         </is>
       </c>
       <c r="C92">
-        <v>4044</v>
+        <v>23451</v>
       </c>
       <c r="D92">
-        <v>10342</v>
+        <v>34298</v>
       </c>
       <c r="E92">
-        <v>32129</v>
+        <v>46964</v>
       </c>
       <c r="F92">
-        <v>62853</v>
+        <v>84798</v>
       </c>
       <c r="G92">
-        <v>83006</v>
+        <v>102791</v>
       </c>
       <c r="H92">
-        <v>87379</v>
+        <v>111756</v>
       </c>
       <c r="I92">
-        <v>108441</v>
+        <v>117362</v>
       </c>
       <c r="J92">
-        <v>123748</v>
+        <v>131631</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -5040,41 +5009,41 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Subprefeitura Lapa	162.031	212.110	257.379	319.806	296.122	270.656	305.526	338.347</t>
+          <t>Vila Sônia	16.028	23.440	32.129	62.853	83.006	87.379	108.441	123.748</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Subprefeitura Lapa</t>
+          <t>Vila Sônia</t>
         </is>
       </c>
       <c r="C93">
-        <v>162031</v>
+        <v>16028</v>
       </c>
       <c r="D93">
-        <v>212110</v>
+        <v>23440</v>
       </c>
       <c r="E93">
-        <v>257379</v>
+        <v>32129</v>
       </c>
       <c r="F93">
-        <v>319806</v>
+        <v>62853</v>
       </c>
       <c r="G93">
-        <v>296122</v>
+        <v>83006</v>
       </c>
       <c r="H93">
-        <v>270656</v>
+        <v>87379</v>
       </c>
       <c r="I93">
-        <v>305526</v>
+        <v>108441</v>
       </c>
       <c r="J93">
-        <v>338347</v>
+        <v>123748</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5084,48 +5053,48 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Subprefeitura Lapa</t>
+          <t>Subprefeitura Butantã</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Barra Funda	11.615	14.041	15.407	17.894	15.977	12.965	14.383	33.436</t>
+          <t>Subprefeitura Lapa	128.530	187.962	257.379	319.806	296.122	270.656	305.526	338.347</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Barra Funda</t>
+          <t>Subprefeitura Lapa</t>
         </is>
       </c>
       <c r="C94">
-        <v>11615</v>
+        <v>128530</v>
       </c>
       <c r="D94">
-        <v>14041</v>
+        <v>187962</v>
       </c>
       <c r="E94">
-        <v>15407</v>
+        <v>257379</v>
       </c>
       <c r="F94">
-        <v>17894</v>
+        <v>319806</v>
       </c>
       <c r="G94">
-        <v>15977</v>
+        <v>296122</v>
       </c>
       <c r="H94">
-        <v>12965</v>
+        <v>270656</v>
       </c>
       <c r="I94">
-        <v>14383</v>
+        <v>305526</v>
       </c>
       <c r="J94">
-        <v>33436</v>
+        <v>338347</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -5142,37 +5111,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Jaguara	5.902	15.976	23.779	32.771	29.798	25.713	24.895	24.730</t>
+          <t>Barra Funda	7.695	11.254	15.407	17.894	15.977	12.965	14.383	33.436</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Jaguara</t>
+          <t>Barra Funda</t>
         </is>
       </c>
       <c r="C95">
-        <v>5902</v>
+        <v>7695</v>
       </c>
       <c r="D95">
-        <v>15976</v>
+        <v>11254</v>
       </c>
       <c r="E95">
-        <v>23779</v>
+        <v>15407</v>
       </c>
       <c r="F95">
-        <v>32771</v>
+        <v>17894</v>
       </c>
       <c r="G95">
-        <v>29798</v>
+        <v>15977</v>
       </c>
       <c r="H95">
-        <v>25713</v>
+        <v>12965</v>
       </c>
       <c r="I95">
-        <v>24895</v>
+        <v>14383</v>
       </c>
       <c r="J95">
-        <v>24730</v>
+        <v>33436</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -5193,37 +5162,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Jaguaré	3.590	8.634	22.080	39.867	44.361	42.479	49.863	55.382</t>
+          <t>Jaguara	11.875	17.367	23.779	32.771	29.798	25.713	24.895	24.730</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Jaguaré</t>
+          <t>Jaguara</t>
         </is>
       </c>
       <c r="C96">
-        <v>3590</v>
+        <v>11875</v>
       </c>
       <c r="D96">
-        <v>8634</v>
+        <v>17367</v>
       </c>
       <c r="E96">
-        <v>22080</v>
+        <v>23779</v>
       </c>
       <c r="F96">
-        <v>39867</v>
+        <v>32771</v>
       </c>
       <c r="G96">
-        <v>44361</v>
+        <v>29798</v>
       </c>
       <c r="H96">
-        <v>42479</v>
+        <v>25713</v>
       </c>
       <c r="I96">
-        <v>49863</v>
+        <v>24895</v>
       </c>
       <c r="J96">
-        <v>55382</v>
+        <v>24730</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -5244,37 +5213,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Lapa	50.904	62.976	70.981	83.705	70.319	60.184	65.739	75.533</t>
+          <t>Jaguaré	11.025	16.124	22.080	39.867	44.361	42.479	49.863	55.382</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lapa</t>
+          <t>Jaguaré</t>
         </is>
       </c>
       <c r="C97">
-        <v>50904</v>
+        <v>11025</v>
       </c>
       <c r="D97">
-        <v>62976</v>
+        <v>16124</v>
       </c>
       <c r="E97">
-        <v>70981</v>
+        <v>22080</v>
       </c>
       <c r="F97">
-        <v>83705</v>
+        <v>39867</v>
       </c>
       <c r="G97">
-        <v>70319</v>
+        <v>44361</v>
       </c>
       <c r="H97">
-        <v>60184</v>
+        <v>42479</v>
       </c>
       <c r="I97">
-        <v>65739</v>
+        <v>49863</v>
       </c>
       <c r="J97">
-        <v>75533</v>
+        <v>55382</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -5295,37 +5264,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Perdizes	71.391	88.320	99.548	117.392	108.840	102.445	111.161	102.391</t>
+          <t>Lapa	35.442	51.835	70.981	83.705	70.319	60.184	65.739	75.533</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Perdizes</t>
+          <t>Lapa</t>
         </is>
       </c>
       <c r="C98">
-        <v>71391</v>
+        <v>35442</v>
       </c>
       <c r="D98">
-        <v>88320</v>
+        <v>51835</v>
       </c>
       <c r="E98">
-        <v>99548</v>
+        <v>70981</v>
       </c>
       <c r="F98">
-        <v>117392</v>
+        <v>83705</v>
       </c>
       <c r="G98">
-        <v>108840</v>
+        <v>70319</v>
       </c>
       <c r="H98">
-        <v>102445</v>
+        <v>60184</v>
       </c>
       <c r="I98">
-        <v>111161</v>
+        <v>65739</v>
       </c>
       <c r="J98">
-        <v>102391</v>
+        <v>75533</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -5346,37 +5315,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Vila Leopoldina	18.629	22.163	25.584	28.177	26.827	26.870	39.485	46.875</t>
+          <t>Perdizes	49.710	72.700	99.548	117.392	108.840	102.445	111.161	102.391</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Vila Leopoldina</t>
+          <t>Perdizes</t>
         </is>
       </c>
       <c r="C99">
-        <v>18629</v>
+        <v>49710</v>
       </c>
       <c r="D99">
-        <v>22163</v>
+        <v>72700</v>
       </c>
       <c r="E99">
-        <v>25584</v>
+        <v>99548</v>
       </c>
       <c r="F99">
-        <v>28177</v>
+        <v>117392</v>
       </c>
       <c r="G99">
-        <v>26827</v>
+        <v>108840</v>
       </c>
       <c r="H99">
-        <v>26870</v>
+        <v>102445</v>
       </c>
       <c r="I99">
-        <v>39485</v>
+        <v>111161</v>
       </c>
       <c r="J99">
-        <v>46875</v>
+        <v>102391</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -5397,41 +5366,41 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Subprefeitura Pinheiros	169.004	247.079	297.644	378.617	339.630	272.574	289.743	285.815</t>
+          <t>Vila Leopoldina	12.783	18.682	25.584	28.177	26.827	26.870	39.485	46.875</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Subprefeitura Pinheiros</t>
+          <t>Vila Leopoldina</t>
         </is>
       </c>
       <c r="C100">
-        <v>169004</v>
+        <v>12783</v>
       </c>
       <c r="D100">
-        <v>247079</v>
+        <v>18682</v>
       </c>
       <c r="E100">
-        <v>297644</v>
+        <v>25584</v>
       </c>
       <c r="F100">
-        <v>378617</v>
+        <v>28177</v>
       </c>
       <c r="G100">
-        <v>339630</v>
+        <v>26827</v>
       </c>
       <c r="H100">
-        <v>272574</v>
+        <v>26870</v>
       </c>
       <c r="I100">
-        <v>289743</v>
+        <v>39485</v>
       </c>
       <c r="J100">
-        <v>285815</v>
+        <v>46875</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -5441,48 +5410,48 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Subprefeitura Pinheiros</t>
+          <t>Subprefeitura Lapa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Alto de Pinheiros	29.529	38.371	44.573	51.178	50.351	44.454	43.117	37.359</t>
+          <t>Subprefeitura Pinheiros	148.645	217.439	297.644	378.617	339.630	272.574	289.743	285.815</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Alto de Pinheiros</t>
+          <t>Subprefeitura Pinheiros</t>
         </is>
       </c>
       <c r="C101">
-        <v>29529</v>
+        <v>148645</v>
       </c>
       <c r="D101">
-        <v>38371</v>
+        <v>217439</v>
       </c>
       <c r="E101">
-        <v>44573</v>
+        <v>297644</v>
       </c>
       <c r="F101">
-        <v>51178</v>
+        <v>378617</v>
       </c>
       <c r="G101">
-        <v>50351</v>
+        <v>339630</v>
       </c>
       <c r="H101">
-        <v>44454</v>
+        <v>272574</v>
       </c>
       <c r="I101">
-        <v>43117</v>
+        <v>289743</v>
       </c>
       <c r="J101">
-        <v>37359</v>
+        <v>285815</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -5499,37 +5468,37 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Itaim Bibi	31.563	61.917	84.923	114.956	107.497	81.456	92.570	101.452</t>
+          <t>Alto de Pinheiros	22.258	32.553	44.573	51.178	50.351	44.454	43.117	37.359</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Itaim Bibi</t>
+          <t>Alto de Pinheiros</t>
         </is>
       </c>
       <c r="C102">
-        <v>31563</v>
+        <v>22258</v>
       </c>
       <c r="D102">
-        <v>61917</v>
+        <v>32553</v>
       </c>
       <c r="E102">
-        <v>84923</v>
+        <v>44573</v>
       </c>
       <c r="F102">
-        <v>114956</v>
+        <v>51178</v>
       </c>
       <c r="G102">
-        <v>107497</v>
+        <v>50351</v>
       </c>
       <c r="H102">
-        <v>81456</v>
+        <v>44454</v>
       </c>
       <c r="I102">
-        <v>92570</v>
+        <v>43117</v>
       </c>
       <c r="J102">
-        <v>101452</v>
+        <v>37359</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -5550,37 +5519,37 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Jardim Paulista	60.681	79.504	91.051	117.804	103.138	83.667	88.692	81.859</t>
+          <t>Itaim Bibi	42.405	62.019	84.923	114.956	107.497	81.456	92.570	101.452</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Jardim Paulista</t>
+          <t>Itaim Bibi</t>
         </is>
       </c>
       <c r="C103">
-        <v>60681</v>
+        <v>42405</v>
       </c>
       <c r="D103">
-        <v>79504</v>
+        <v>62019</v>
       </c>
       <c r="E103">
-        <v>91051</v>
+        <v>84923</v>
       </c>
       <c r="F103">
-        <v>117804</v>
+        <v>114956</v>
       </c>
       <c r="G103">
-        <v>103138</v>
+        <v>107497</v>
       </c>
       <c r="H103">
-        <v>83667</v>
+        <v>81456</v>
       </c>
       <c r="I103">
-        <v>88692</v>
+        <v>92570</v>
       </c>
       <c r="J103">
-        <v>81859</v>
+        <v>101452</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -5601,37 +5570,37 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Pinheiros	47.231	67.287	77.097	94.679	78.644	62.997	65.364	65.145</t>
+          <t>Jardim Paulista	45.462	66.489	91.051	117.804	103.138	83.667	88.692	81.859</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Pinheiros</t>
+          <t>Jardim Paulista</t>
         </is>
       </c>
       <c r="C104">
-        <v>47231</v>
+        <v>45462</v>
       </c>
       <c r="D104">
-        <v>67287</v>
+        <v>66489</v>
       </c>
       <c r="E104">
-        <v>77097</v>
+        <v>91051</v>
       </c>
       <c r="F104">
-        <v>94679</v>
+        <v>117804</v>
       </c>
       <c r="G104">
-        <v>78644</v>
+        <v>103138</v>
       </c>
       <c r="H104">
-        <v>62997</v>
+        <v>83667</v>
       </c>
       <c r="I104">
-        <v>65364</v>
+        <v>88692</v>
       </c>
       <c r="J104">
-        <v>65145</v>
+        <v>81859</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -5652,46 +5621,46 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Região Sul	406.301	746.051	1.417.546	2.317.589	2.772.187	3.211.818	3.586.020	3.735.554</t>
+          <t>Pinheiros	38.520	56.378	77.097	94.679	78.644	62.997	65.364	65.145</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Região Sul</t>
+          <t>Pinheiros</t>
         </is>
       </c>
       <c r="C105">
-        <v>406301</v>
+        <v>38520</v>
       </c>
       <c r="D105">
-        <v>746051</v>
+        <v>56378</v>
       </c>
       <c r="E105">
-        <v>1417546</v>
+        <v>77097</v>
       </c>
       <c r="F105">
-        <v>2317589</v>
+        <v>94679</v>
       </c>
       <c r="G105">
-        <v>2772187</v>
+        <v>78644</v>
       </c>
       <c r="H105">
-        <v>3211818</v>
+        <v>62997</v>
       </c>
       <c r="I105">
-        <v>3586020</v>
+        <v>65364</v>
       </c>
       <c r="J105">
-        <v>3735554</v>
+        <v>65145</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Região</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Região Sul</t>
+          <t>Região Oeste</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -5703,41 +5672,41 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Subprefeitura Campo Limpo	12.702	34.810	123.903	261.334	395.544	505.969	607.105	675.598</t>
+          <t>Região Sul	406.301	746.051	1.417.546	2.317.589	2.772.187	3.211.818	3.586.020	3.735.554</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Subprefeitura Campo Limpo</t>
+          <t>Região Sul</t>
         </is>
       </c>
       <c r="C106">
-        <v>12702</v>
+        <v>406301</v>
       </c>
       <c r="D106">
-        <v>34810</v>
+        <v>746051</v>
       </c>
       <c r="E106">
-        <v>123903</v>
+        <v>1417546</v>
       </c>
       <c r="F106">
-        <v>261334</v>
+        <v>2317589</v>
       </c>
       <c r="G106">
-        <v>395544</v>
+        <v>2772187</v>
       </c>
       <c r="H106">
-        <v>505969</v>
+        <v>3211818</v>
       </c>
       <c r="I106">
-        <v>607105</v>
+        <v>3586020</v>
       </c>
       <c r="J106">
-        <v>675598</v>
+        <v>3735554</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Região</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -5747,48 +5716,48 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Subprefeitura Campo Limpo</t>
+          <t>Subprefeitura Pinheiros</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Campo Limpo	5.932	15.803	54.555	110.556	159.471	191.527	211.361	236.162</t>
+          <t>Subprefeitura Campo Limpo	35.531	65.253	123.903	261.334	395.544	505.969	607.105	675.598</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Campo Limpo</t>
+          <t>Subprefeitura Campo Limpo</t>
         </is>
       </c>
       <c r="C107">
-        <v>5932</v>
+        <v>35531</v>
       </c>
       <c r="D107">
-        <v>15803</v>
+        <v>65253</v>
       </c>
       <c r="E107">
-        <v>54555</v>
+        <v>123903</v>
       </c>
       <c r="F107">
-        <v>110556</v>
+        <v>261334</v>
       </c>
       <c r="G107">
-        <v>159471</v>
+        <v>395544</v>
       </c>
       <c r="H107">
-        <v>191527</v>
+        <v>505969</v>
       </c>
       <c r="I107">
-        <v>211361</v>
+        <v>607105</v>
       </c>
       <c r="J107">
-        <v>236162</v>
+        <v>675598</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -5805,37 +5774,37 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Capão Redondo	5.153	14.536	57.259	128.194	193.497	240.793	268.729	270.767</t>
+          <t>Campo Limpo	15.645	28.732	54.555	110.556	159.471	191.527	211.361	236.162</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Capão Redondo</t>
+          <t>Campo Limpo</t>
         </is>
       </c>
       <c r="C108">
-        <v>5153</v>
+        <v>15645</v>
       </c>
       <c r="D108">
-        <v>14536</v>
+        <v>28732</v>
       </c>
       <c r="E108">
-        <v>57259</v>
+        <v>54555</v>
       </c>
       <c r="F108">
-        <v>128194</v>
+        <v>110556</v>
       </c>
       <c r="G108">
-        <v>193497</v>
+        <v>159471</v>
       </c>
       <c r="H108">
-        <v>240793</v>
+        <v>191527</v>
       </c>
       <c r="I108">
-        <v>268729</v>
+        <v>211361</v>
       </c>
       <c r="J108">
-        <v>270767</v>
+        <v>236162</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -5856,37 +5825,37 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Vila Andrade	1.617	4.471	12.089	22.584	42.576	73.649	127.015	168.669</t>
+          <t>Capão Redondo	16.421	30.157	57.259	128.194	193.497	240.793	268.729	270.767</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Vila Andrade</t>
+          <t>Capão Redondo</t>
         </is>
       </c>
       <c r="C109">
-        <v>1617</v>
+        <v>16421</v>
       </c>
       <c r="D109">
-        <v>4471</v>
+        <v>30157</v>
       </c>
       <c r="E109">
-        <v>12089</v>
+        <v>57259</v>
       </c>
       <c r="F109">
-        <v>22584</v>
+        <v>128194</v>
       </c>
       <c r="G109">
-        <v>42576</v>
+        <v>193497</v>
       </c>
       <c r="H109">
-        <v>73649</v>
+        <v>240793</v>
       </c>
       <c r="I109">
-        <v>127015</v>
+        <v>268729</v>
       </c>
       <c r="J109">
-        <v>168669</v>
+        <v>270767</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -5907,41 +5876,41 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Subprefeitura Capela do Socorro	65.822	19.347	103.793	281.029	405.769	563.922	594.930	605.383</t>
+          <t>Vila Andrade	3.465	6.364	12.089	22.584	42.576	73.649	127.015	168.669</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Subprefeitura Capela do Socorro</t>
+          <t>Vila Andrade</t>
         </is>
       </c>
       <c r="C110">
-        <v>65822</v>
+        <v>3465</v>
       </c>
       <c r="D110">
-        <v>19347</v>
+        <v>6364</v>
       </c>
       <c r="E110">
-        <v>103793</v>
+        <v>12089</v>
       </c>
       <c r="F110">
-        <v>281029</v>
+        <v>22584</v>
       </c>
       <c r="G110">
-        <v>405769</v>
+        <v>42576</v>
       </c>
       <c r="H110">
-        <v>563922</v>
+        <v>73649</v>
       </c>
       <c r="I110">
-        <v>594930</v>
+        <v>127015</v>
       </c>
       <c r="J110">
-        <v>605383</v>
+        <v>168669</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -5951,48 +5920,48 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Subprefeitura Capela do Socorro</t>
+          <t>Subprefeitura Campo Limpo</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Cidade Dutra	2.135	7.781	45.168	122.990	168.821	191.389	196.360	182.459</t>
+          <t>Subprefeitura Capela do Socorro	29.765	54.662	103.793	281.029	405.769	563.922	594.930	605.383</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cidade Dutra</t>
+          <t>Subprefeitura Capela do Socorro</t>
         </is>
       </c>
       <c r="C111">
-        <v>2135</v>
+        <v>29765</v>
       </c>
       <c r="D111">
-        <v>7781</v>
+        <v>54662</v>
       </c>
       <c r="E111">
-        <v>45168</v>
+        <v>103793</v>
       </c>
       <c r="F111">
-        <v>122990</v>
+        <v>281029</v>
       </c>
       <c r="G111">
-        <v>168821</v>
+        <v>405769</v>
       </c>
       <c r="H111">
-        <v>191389</v>
+        <v>563922</v>
       </c>
       <c r="I111">
-        <v>196360</v>
+        <v>594930</v>
       </c>
       <c r="J111">
-        <v>182459</v>
+        <v>605383</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6009,37 +5978,37 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Grajaú	3.740	8.989	43.664	117.301	193.754	333.436	360.787	384.873</t>
+          <t>Cidade Dutra	12.953	23.788	45.168	122.990	168.821	191.389	196.360	182.459</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Grajaú</t>
+          <t>Cidade Dutra</t>
         </is>
       </c>
       <c r="C112">
-        <v>3740</v>
+        <v>12953</v>
       </c>
       <c r="D112">
-        <v>8989</v>
+        <v>23788</v>
       </c>
       <c r="E112">
-        <v>43664</v>
+        <v>45168</v>
       </c>
       <c r="F112">
-        <v>117301</v>
+        <v>122990</v>
       </c>
       <c r="G112">
-        <v>193754</v>
+        <v>168821</v>
       </c>
       <c r="H112">
-        <v>333436</v>
+        <v>191389</v>
       </c>
       <c r="I112">
-        <v>360787</v>
+        <v>196360</v>
       </c>
       <c r="J112">
-        <v>384873</v>
+        <v>182459</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -6060,37 +6029,37 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Socorro	707	2.577	14.961	40.738	43.194	39.097	37.783	38.051</t>
+          <t>Grajaú	12.521	22.995	43.664	117.301	193.754	333.436	360.787	384.873</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Socorro</t>
+          <t>Grajaú</t>
         </is>
       </c>
       <c r="C113">
-        <v>707</v>
+        <v>12521</v>
       </c>
       <c r="D113">
-        <v>2577</v>
+        <v>22995</v>
       </c>
       <c r="E113">
-        <v>14961</v>
+        <v>43664</v>
       </c>
       <c r="F113">
-        <v>40738</v>
+        <v>117301</v>
       </c>
       <c r="G113">
-        <v>43194</v>
+        <v>193754</v>
       </c>
       <c r="H113">
-        <v>39097</v>
+        <v>333436</v>
       </c>
       <c r="I113">
-        <v>37783</v>
+        <v>360787</v>
       </c>
       <c r="J113">
-        <v>38051</v>
+        <v>384873</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -6111,41 +6080,41 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Subprefeitura Cidade Ademar	20.415	51.348	153.255	282.707	316.795	370.797	410.998	412.804</t>
+          <t>Socorro	4.291	7.879	14.961	40.738	43.194	39.097	37.783	38.051</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Subprefeitura Cidade Ademar</t>
+          <t>Socorro</t>
         </is>
       </c>
       <c r="C114">
-        <v>20415</v>
+        <v>4291</v>
       </c>
       <c r="D114">
-        <v>51348</v>
+        <v>7879</v>
       </c>
       <c r="E114">
-        <v>153255</v>
+        <v>14961</v>
       </c>
       <c r="F114">
-        <v>282707</v>
+        <v>40738</v>
       </c>
       <c r="G114">
-        <v>316795</v>
+        <v>43194</v>
       </c>
       <c r="H114">
-        <v>370797</v>
+        <v>39097</v>
       </c>
       <c r="I114">
-        <v>410998</v>
+        <v>37783</v>
       </c>
       <c r="J114">
-        <v>412804</v>
+        <v>38051</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -6155,48 +6124,48 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Subprefeitura Cidade Ademar</t>
+          <t>Subprefeitura Capela do Socorro</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Cidade Ademar	17.031	42.335	122.138	219.649	230.794	243.143	265.471	249.218</t>
+          <t>Subprefeitura Cidade Ademar	43.951	80.716	153.255	282.707	316.795	370.797	410.998	412.804</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Cidade Ademar</t>
+          <t>Subprefeitura Cidade Ademar</t>
         </is>
       </c>
       <c r="C115">
-        <v>17031</v>
+        <v>43951</v>
       </c>
       <c r="D115">
-        <v>42335</v>
+        <v>80716</v>
       </c>
       <c r="E115">
-        <v>122138</v>
+        <v>153255</v>
       </c>
       <c r="F115">
-        <v>219649</v>
+        <v>282707</v>
       </c>
       <c r="G115">
-        <v>230794</v>
+        <v>316795</v>
       </c>
       <c r="H115">
-        <v>243143</v>
+        <v>370797</v>
       </c>
       <c r="I115">
-        <v>265471</v>
+        <v>410998</v>
       </c>
       <c r="J115">
-        <v>249218</v>
+        <v>412804</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -6213,37 +6182,37 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Pedreira	3.384	9.013	31.117	63.058	86.001	127.654	145.527	163.586</t>
+          <t>Cidade Ademar	35.021	64.316	122.138	219.649	230.794	243.143	265.471	249.218</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Pedreira</t>
+          <t>Cidade Ademar</t>
         </is>
       </c>
       <c r="C116">
-        <v>3384</v>
+        <v>35021</v>
       </c>
       <c r="D116">
-        <v>9013</v>
+        <v>64316</v>
       </c>
       <c r="E116">
-        <v>31117</v>
+        <v>122138</v>
       </c>
       <c r="F116">
-        <v>63058</v>
+        <v>219649</v>
       </c>
       <c r="G116">
-        <v>86001</v>
+        <v>230794</v>
       </c>
       <c r="H116">
-        <v>127654</v>
+        <v>243143</v>
       </c>
       <c r="I116">
-        <v>145527</v>
+        <v>265471</v>
       </c>
       <c r="J116">
-        <v>163586</v>
+        <v>249218</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -6264,41 +6233,41 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Subprefeitura Ipiranga	190.612	272.223	344.958	398.028	423.168	429.182	463.804	480.878</t>
+          <t>Pedreira	8.930	16.400	31.117	63.058	86.001	127.654	145.527	163.586</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Subprefeitura Ipiranga</t>
+          <t>Pedreira</t>
         </is>
       </c>
       <c r="C117">
-        <v>190612</v>
+        <v>8930</v>
       </c>
       <c r="D117">
-        <v>272223</v>
+        <v>16400</v>
       </c>
       <c r="E117">
-        <v>344958</v>
+        <v>31117</v>
       </c>
       <c r="F117">
-        <v>398028</v>
+        <v>63058</v>
       </c>
       <c r="G117">
-        <v>423168</v>
+        <v>86001</v>
       </c>
       <c r="H117">
-        <v>429182</v>
+        <v>127654</v>
       </c>
       <c r="I117">
-        <v>463804</v>
+        <v>145527</v>
       </c>
       <c r="J117">
-        <v>480878</v>
+        <v>163586</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -6308,48 +6277,48 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Subprefeitura Ipiranga</t>
+          <t>Subprefeitura Cidade Ademar</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Cursino	25.463	52.021	90.462	116.473	110.435	102.036	109.088	103.171</t>
+          <t>Subprefeitura Ipiranga	98.921	181.671	344.958	398.028	423.168	429.182	463.804	480.878</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Cursino</t>
+          <t>Subprefeitura Ipiranga</t>
         </is>
       </c>
       <c r="C118">
-        <v>25463</v>
+        <v>98921</v>
       </c>
       <c r="D118">
-        <v>52021</v>
+        <v>181671</v>
       </c>
       <c r="E118">
-        <v>90462</v>
+        <v>344958</v>
       </c>
       <c r="F118">
-        <v>116473</v>
+        <v>398028</v>
       </c>
       <c r="G118">
-        <v>110435</v>
+        <v>423168</v>
       </c>
       <c r="H118">
-        <v>102036</v>
+        <v>429182</v>
       </c>
       <c r="I118">
-        <v>109088</v>
+        <v>463804</v>
       </c>
       <c r="J118">
-        <v>103171</v>
+        <v>480878</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -6366,37 +6335,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ipiranga	94.691	109.546	111.939	117.588	101.533	98.863	106.865	116.271</t>
+          <t>Cursino	25.942	47.643	90.462	116.473	110.435	102.036	109.088	103.171</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ipiranga</t>
+          <t>Cursino</t>
         </is>
       </c>
       <c r="C119">
-        <v>94691</v>
+        <v>25942</v>
       </c>
       <c r="D119">
-        <v>109546</v>
+        <v>47643</v>
       </c>
       <c r="E119">
-        <v>111939</v>
+        <v>90462</v>
       </c>
       <c r="F119">
-        <v>117588</v>
+        <v>116473</v>
       </c>
       <c r="G119">
-        <v>101533</v>
+        <v>110435</v>
       </c>
       <c r="H119">
-        <v>98863</v>
+        <v>102036</v>
       </c>
       <c r="I119">
-        <v>106865</v>
+        <v>109088</v>
       </c>
       <c r="J119">
-        <v>116271</v>
+        <v>103171</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -6417,37 +6386,37 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sacomã	70.458	110.656	142.557	163.967	211.200	228.283	247.851	261.436</t>
+          <t>Ipiranga	32.101	58.954	111.939	117.588	101.533	98.863	106.865	116.271</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sacomã</t>
+          <t>Ipiranga</t>
         </is>
       </c>
       <c r="C120">
-        <v>70458</v>
+        <v>32101</v>
       </c>
       <c r="D120">
-        <v>110656</v>
+        <v>58954</v>
       </c>
       <c r="E120">
-        <v>142557</v>
+        <v>111939</v>
       </c>
       <c r="F120">
-        <v>163967</v>
+        <v>117588</v>
       </c>
       <c r="G120">
-        <v>211200</v>
+        <v>101533</v>
       </c>
       <c r="H120">
-        <v>228283</v>
+        <v>98863</v>
       </c>
       <c r="I120">
-        <v>247851</v>
+        <v>106865</v>
       </c>
       <c r="J120">
-        <v>261436</v>
+        <v>116271</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -6468,41 +6437,41 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Subprefeitura Jabaquara	26.854	72.546	141.762	196.151	214.350	214.148	223.780	214.958</t>
+          <t>Sacomã	40.878	75.074	142.557	163.967	211.200	228.283	247.851	261.436</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Subprefeitura Jabaquara</t>
+          <t>Sacomã</t>
         </is>
       </c>
       <c r="C121">
-        <v>26854</v>
+        <v>40878</v>
       </c>
       <c r="D121">
-        <v>72546</v>
+        <v>75074</v>
       </c>
       <c r="E121">
-        <v>141762</v>
+        <v>142557</v>
       </c>
       <c r="F121">
-        <v>196151</v>
+        <v>163967</v>
       </c>
       <c r="G121">
-        <v>214350</v>
+        <v>211200</v>
       </c>
       <c r="H121">
-        <v>214148</v>
+        <v>228283</v>
       </c>
       <c r="I121">
-        <v>223780</v>
+        <v>247851</v>
       </c>
       <c r="J121">
-        <v>214958</v>
+        <v>261436</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -6512,26 +6481,26 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Subprefeitura Jabaquara</t>
+          <t>Subprefeitura Ipiranga</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Jabaquara	26.854	72.546	141.762	196.151	214.350	214.148	223.780	214.958</t>
+          <t>Subprefeitura Jabaquara	40.651	74.656	141.762	196.151	214.350	214.148	223.780	214.958</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Jabaquara</t>
+          <t>Subprefeitura Jabaquara</t>
         </is>
       </c>
       <c r="C122">
-        <v>26854</v>
+        <v>40651</v>
       </c>
       <c r="D122">
-        <v>72546</v>
+        <v>74656</v>
       </c>
       <c r="E122">
         <v>141762</v>
@@ -6553,7 +6522,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -6570,41 +6539,41 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Subprefeitura M Boi Mirim	10.903	30.754	121.141	271.214	382.657	484.966	563.305	570.809</t>
+          <t>Jabaquara	40.651	74.656	141.762	196.151	214.350	214.148	223.780	214.958</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Subprefeitura M Boi Mirim</t>
+          <t>Jabaquara</t>
         </is>
       </c>
       <c r="C123">
-        <v>10903</v>
+        <v>40651</v>
       </c>
       <c r="D123">
-        <v>30754</v>
+        <v>74656</v>
       </c>
       <c r="E123">
-        <v>121141</v>
+        <v>141762</v>
       </c>
       <c r="F123">
-        <v>271214</v>
+        <v>196151</v>
       </c>
       <c r="G123">
-        <v>382657</v>
+        <v>214350</v>
       </c>
       <c r="H123">
-        <v>484966</v>
+        <v>214148</v>
       </c>
       <c r="I123">
-        <v>563305</v>
+        <v>223780</v>
       </c>
       <c r="J123">
-        <v>570809</v>
+        <v>214958</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -6614,48 +6583,48 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Subprefeitura M Boi Mirim</t>
+          <t>Subprefeitura Jabaquara</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Jardim Ângela	4.325	12.199	48.052	107.580	178.373	245.805	295.434	311.432</t>
+          <t>Subprefeitura M Boi Mirim	34.741	63.802	121.141	271.214	382.657	484.966	563.305	570.809</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Jardim Ângela</t>
+          <t>Subprefeitura M Boi Mirim</t>
         </is>
       </c>
       <c r="C124">
-        <v>4325</v>
+        <v>34741</v>
       </c>
       <c r="D124">
-        <v>12199</v>
+        <v>63802</v>
       </c>
       <c r="E124">
-        <v>48052</v>
+        <v>121141</v>
       </c>
       <c r="F124">
-        <v>107580</v>
+        <v>271214</v>
       </c>
       <c r="G124">
-        <v>178373</v>
+        <v>382657</v>
       </c>
       <c r="H124">
-        <v>245805</v>
+        <v>484966</v>
       </c>
       <c r="I124">
-        <v>295434</v>
+        <v>563305</v>
       </c>
       <c r="J124">
-        <v>311432</v>
+        <v>570809</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -6672,37 +6641,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Jardim São Luís	6.578	18.555	73.089	163.634	204.284	239.161	267.871	259.377</t>
+          <t>Jardim Ângela	13.781	25.309	48.052	107.580	178.373	245.805	295.434	311.432</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Jardim São Luís</t>
+          <t>Jardim Ângela</t>
         </is>
       </c>
       <c r="C125">
-        <v>6578</v>
+        <v>13781</v>
       </c>
       <c r="D125">
-        <v>18555</v>
+        <v>25309</v>
       </c>
       <c r="E125">
-        <v>73089</v>
+        <v>48052</v>
       </c>
       <c r="F125">
-        <v>163634</v>
+        <v>107580</v>
       </c>
       <c r="G125">
-        <v>204284</v>
+        <v>178373</v>
       </c>
       <c r="H125">
-        <v>239161</v>
+        <v>245805</v>
       </c>
       <c r="I125">
-        <v>267871</v>
+        <v>295434</v>
       </c>
       <c r="J125">
-        <v>259377</v>
+        <v>311432</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -6723,41 +6692,41 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Subprefeitura Parelheiros	1.759	3.328	13.664	36.150	61.586	111.240	139.441	165.138</t>
+          <t>Jardim São Luís	20.960	38.493	73.089	163.634	204.284	239.161	267.871	259.377</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Subprefeitura Parelheiros</t>
+          <t>Jardim São Luís</t>
         </is>
       </c>
       <c r="C126">
-        <v>1759</v>
+        <v>20960</v>
       </c>
       <c r="D126">
-        <v>3328</v>
+        <v>38493</v>
       </c>
       <c r="E126">
-        <v>13664</v>
+        <v>73089</v>
       </c>
       <c r="F126">
-        <v>36150</v>
+        <v>163634</v>
       </c>
       <c r="G126">
-        <v>61586</v>
+        <v>204284</v>
       </c>
       <c r="H126">
-        <v>111240</v>
+        <v>239161</v>
       </c>
       <c r="I126">
-        <v>139441</v>
+        <v>267871</v>
       </c>
       <c r="J126">
-        <v>165138</v>
+        <v>259377</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -6767,48 +6736,48 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Subprefeitura Parelheiros</t>
+          <t>Subprefeitura M Boi Mirim</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Marsilac	1.209	1.322	2.018	4.439	5.992	8.404	8.258	11.443</t>
+          <t>Subprefeitura Parelheiros	3.918	7.195	13.664	36.150	61.586	111.240	139.441	165.138</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Marsilac</t>
+          <t>Subprefeitura Parelheiros</t>
         </is>
       </c>
       <c r="C127">
-        <v>1209</v>
+        <v>3918</v>
       </c>
       <c r="D127">
-        <v>1322</v>
+        <v>7195</v>
       </c>
       <c r="E127">
-        <v>2018</v>
+        <v>13664</v>
       </c>
       <c r="F127">
-        <v>4439</v>
+        <v>36150</v>
       </c>
       <c r="G127">
-        <v>5992</v>
+        <v>61586</v>
       </c>
       <c r="H127">
-        <v>8404</v>
+        <v>111240</v>
       </c>
       <c r="I127">
-        <v>8258</v>
+        <v>139441</v>
       </c>
       <c r="J127">
-        <v>11443</v>
+        <v>165138</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -6825,37 +6794,37 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Parelheiros	550	2.006	11.646	31.711	55.594	102.836	131.183	153.695</t>
+          <t>Marsilac	579	1.063	2.018	4.439	5.992	8.404	8.258	11.443</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Parelheiros</t>
+          <t>Marsilac</t>
         </is>
       </c>
       <c r="C128">
-        <v>550</v>
+        <v>579</v>
       </c>
       <c r="D128">
-        <v>2006</v>
+        <v>1063</v>
       </c>
       <c r="E128">
-        <v>11646</v>
+        <v>2018</v>
       </c>
       <c r="F128">
-        <v>31711</v>
+        <v>4439</v>
       </c>
       <c r="G128">
-        <v>55594</v>
+        <v>5992</v>
       </c>
       <c r="H128">
-        <v>102836</v>
+        <v>8404</v>
       </c>
       <c r="I128">
-        <v>131183</v>
+        <v>8258</v>
       </c>
       <c r="J128">
-        <v>153695</v>
+        <v>11443</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -6876,41 +6845,41 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Subprefeitura Santo Amaro	19.038	60.218	137.065	239.371	235.560	218.558	238.025	272.332</t>
+          <t>Parelheiros	3.339	6.132	11.646	31.711	55.594	102.836	131.183	153.695</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Subprefeitura Santo Amaro</t>
+          <t>Parelheiros</t>
         </is>
       </c>
       <c r="C129">
-        <v>19038</v>
+        <v>3339</v>
       </c>
       <c r="D129">
-        <v>60218</v>
+        <v>6132</v>
       </c>
       <c r="E129">
-        <v>137065</v>
+        <v>11646</v>
       </c>
       <c r="F129">
-        <v>239371</v>
+        <v>31711</v>
       </c>
       <c r="G129">
-        <v>235560</v>
+        <v>55594</v>
       </c>
       <c r="H129">
-        <v>218558</v>
+        <v>102836</v>
       </c>
       <c r="I129">
-        <v>238025</v>
+        <v>131183</v>
       </c>
       <c r="J129">
-        <v>272332</v>
+        <v>153695</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -6920,48 +6889,48 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Subprefeitura Santo Amaro</t>
+          <t>Subprefeitura Parelheiros</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Campo Belo	9.171	32.275	52.959	75.631	77.952	66.646	65.752	71.058</t>
+          <t>Subprefeitura Santo Amaro	39.310	72.193	137.065	239.371	235.560	218.558	238.025	272.332</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Campo Belo</t>
+          <t>Subprefeitura Santo Amaro</t>
         </is>
       </c>
       <c r="C130">
-        <v>9171</v>
+        <v>39310</v>
       </c>
       <c r="D130">
-        <v>32275</v>
+        <v>72193</v>
       </c>
       <c r="E130">
-        <v>52959</v>
+        <v>137065</v>
       </c>
       <c r="F130">
-        <v>75631</v>
+        <v>239371</v>
       </c>
       <c r="G130">
-        <v>77952</v>
+        <v>235560</v>
       </c>
       <c r="H130">
-        <v>66646</v>
+        <v>218558</v>
       </c>
       <c r="I130">
-        <v>65752</v>
+        <v>238025</v>
       </c>
       <c r="J130">
-        <v>71058</v>
+        <v>272332</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -6978,37 +6947,37 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Campo Grande	3.782	10.075	34.782	70.485	82.052	91.373	100.713	115.925</t>
+          <t>Campo Belo	15.187	27.892	52.959	75.631	77.952	66.646	65.752	71.058</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Campo Grande</t>
+          <t>Campo Belo</t>
         </is>
       </c>
       <c r="C131">
-        <v>3782</v>
+        <v>15187</v>
       </c>
       <c r="D131">
-        <v>10075</v>
+        <v>27892</v>
       </c>
       <c r="E131">
-        <v>34782</v>
+        <v>52959</v>
       </c>
       <c r="F131">
-        <v>70485</v>
+        <v>75631</v>
       </c>
       <c r="G131">
-        <v>82052</v>
+        <v>77952</v>
       </c>
       <c r="H131">
-        <v>91373</v>
+        <v>66646</v>
       </c>
       <c r="I131">
-        <v>100713</v>
+        <v>65752</v>
       </c>
       <c r="J131">
-        <v>115925</v>
+        <v>71058</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -7029,37 +6998,37 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Santo Amaro	6.085	17.868	49.324	93.255	75.556	60.539	71.560	85.349</t>
+          <t>Campo Grande	9.975	18.319	34.782	70.485	82.052	91.373	100.713	115.925</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Campo Grande</t>
         </is>
       </c>
       <c r="C132">
-        <v>6085</v>
+        <v>9975</v>
       </c>
       <c r="D132">
-        <v>17868</v>
+        <v>18319</v>
       </c>
       <c r="E132">
-        <v>49324</v>
+        <v>34782</v>
       </c>
       <c r="F132">
-        <v>93255</v>
+        <v>70485</v>
       </c>
       <c r="G132">
-        <v>75556</v>
+        <v>82052</v>
       </c>
       <c r="H132">
-        <v>60539</v>
+        <v>91373</v>
       </c>
       <c r="I132">
-        <v>71560</v>
+        <v>100713</v>
       </c>
       <c r="J132">
-        <v>85349</v>
+        <v>115925</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -7080,41 +7049,41 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Subprefeitura Vila Mariana	117.436	201.477	278.005	351.605	336.758	313.036	344.632	337.654</t>
+          <t>Santo Amaro	14.148	25.982	49.324	93.255	75.556	60.539	71.560	85.349</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Subprefeitura Vila Mariana</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="C133">
-        <v>117436</v>
+        <v>14148</v>
       </c>
       <c r="D133">
-        <v>201477</v>
+        <v>25982</v>
       </c>
       <c r="E133">
-        <v>278005</v>
+        <v>49324</v>
       </c>
       <c r="F133">
-        <v>351605</v>
+        <v>93255</v>
       </c>
       <c r="G133">
-        <v>336758</v>
+        <v>75556</v>
       </c>
       <c r="H133">
-        <v>313036</v>
+        <v>60539</v>
       </c>
       <c r="I133">
-        <v>344632</v>
+        <v>71560</v>
       </c>
       <c r="J133">
-        <v>337654</v>
+        <v>85349</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Subprefeitura</t>
+          <t>Distrito</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -7124,48 +7093,48 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Subprefeitura Vila Mariana</t>
+          <t>Subprefeitura Santo Amaro</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Moema	33.988	49.620	57.375	72.162	77.340	71.276	83.368	81.899</t>
+          <t>Subprefeitura Vila Mariana	79.721	146.411	278.005	351.605	336.758	313.036	344.632	337.654</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Moema</t>
+          <t>Subprefeitura Vila Mariana</t>
         </is>
       </c>
       <c r="C134">
-        <v>33988</v>
+        <v>79721</v>
       </c>
       <c r="D134">
-        <v>49620</v>
+        <v>146411</v>
       </c>
       <c r="E134">
-        <v>57375</v>
+        <v>278005</v>
       </c>
       <c r="F134">
-        <v>72162</v>
+        <v>351605</v>
       </c>
       <c r="G134">
-        <v>77340</v>
+        <v>336758</v>
       </c>
       <c r="H134">
-        <v>71276</v>
+        <v>313036</v>
       </c>
       <c r="I134">
-        <v>83368</v>
+        <v>344632</v>
       </c>
       <c r="J134">
-        <v>81899</v>
+        <v>337654</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Distrito</t>
+          <t>Subprefeitura</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -7182,37 +7151,37 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Saúde	29.011	63.139	104.872	136.221	126.596	118.077	130.780	128.469</t>
+          <t>Moema	16.452	30.215	57.375	72.162	77.340	71.276	83.368	81.899</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>Moema</t>
         </is>
       </c>
       <c r="C135">
-        <v>29011</v>
+        <v>16452</v>
       </c>
       <c r="D135">
-        <v>63139</v>
+        <v>30215</v>
       </c>
       <c r="E135">
-        <v>104872</v>
+        <v>57375</v>
       </c>
       <c r="F135">
-        <v>136221</v>
+        <v>72162</v>
       </c>
       <c r="G135">
-        <v>126596</v>
+        <v>77340</v>
       </c>
       <c r="H135">
-        <v>118077</v>
+        <v>71276</v>
       </c>
       <c r="I135">
-        <v>130780</v>
+        <v>83368</v>
       </c>
       <c r="J135">
-        <v>128469</v>
+        <v>81899</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -7233,49 +7202,100 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Vila Mariana	54.437	88.718	115.758	143.222	132.822	123.683	130.484	127.286</t>
+          <t>Saúde	30.075	55.233	104.872	136.221	126.596	118.077	130.780	128.469</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
+          <t>Saúde</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>30075</v>
+      </c>
+      <c r="D136">
+        <v>55233</v>
+      </c>
+      <c r="E136">
+        <v>104872</v>
+      </c>
+      <c r="F136">
+        <v>136221</v>
+      </c>
+      <c r="G136">
+        <v>126596</v>
+      </c>
+      <c r="H136">
+        <v>118077</v>
+      </c>
+      <c r="I136">
+        <v>130780</v>
+      </c>
+      <c r="J136">
+        <v>128469</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Distrito</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Região Sul</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Subprefeitura Vila Mariana</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Vila Mariana	33.194	60.963	115.758	143.222	132.822	123.683	130.484	127.286</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
           <t>Vila Mariana</t>
         </is>
       </c>
-      <c r="C136">
-        <v>54437</v>
-      </c>
-      <c r="D136">
-        <v>88718</v>
-      </c>
-      <c r="E136">
+      <c r="C137">
+        <v>33194</v>
+      </c>
+      <c r="D137">
+        <v>60963</v>
+      </c>
+      <c r="E137">
         <v>115758</v>
       </c>
-      <c r="F136">
+      <c r="F137">
         <v>143222</v>
       </c>
-      <c r="G136">
+      <c r="G137">
         <v>132822</v>
       </c>
-      <c r="H136">
+      <c r="H137">
         <v>123683</v>
       </c>
-      <c r="I136">
+      <c r="I137">
         <v>130484</v>
       </c>
-      <c r="J136">
+      <c r="J137">
         <v>127286</v>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>Distrito</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Distrito</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
         <is>
           <t>Região Sul</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t>Subprefeitura Vila Mariana</t>
         </is>
